--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -57,13 +57,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-17T15:32:01+00:00</t>
+    <t>2023-10-31T15:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>JPSys</t>
+    <t>VA</t>
   </si>
   <si>
     <t>Contact</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31T15:37:13+00:00</t>
+    <t>2023-11-01T18:52:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for Use Case Location</t>
+    <t>This StructureDefinition contains the maps for VistA HOSPITAL LOCATION (file 44) to FHIR Location</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2907" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2905" uniqueCount="483">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-01T18:52:48+00:00</t>
+    <t>2023-11-08T21:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -555,10 +555,7 @@
     <t>The status property covers the general availability of the resource, not the current value which may be covered by the operationStatus, or by a schedule/slots if they are configured for the location.</t>
   </si>
   <si>
-    <t>Indicates whether the location is still in use.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/location-status|4.0.1</t>
+    <t>http://va.gov/fhir/ValueSet/VFLocationStatus</t>
   </si>
   <si>
     <t>.statusCode</t>
@@ -3993,11 +3990,9 @@
       <c r="X19" t="s" s="2">
         <v>125</v>
       </c>
-      <c r="Y19" t="s" s="2">
+      <c r="Y19" s="2"/>
+      <c r="Z19" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="Z19" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>35</v>
@@ -4030,24 +4025,24 @@
         <v>56</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AL19" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="AL19" t="s" s="2">
+      <c r="AM19" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>176</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4070,13 +4065,13 @@
         <v>45</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4106,11 +4101,11 @@
         <v>68</v>
       </c>
       <c r="Y20" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="Z20" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="Z20" t="s" s="2">
-        <v>182</v>
-      </c>
       <c r="AA20" t="s" s="2">
         <v>35</v>
       </c>
@@ -4127,7 +4122,7 @@
         <v>35</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>36</v>
@@ -4145,7 +4140,7 @@
         <v>113</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>35</v>
@@ -4156,10 +4151,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4185,13 +4180,13 @@
         <v>109</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>186</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4241,7 +4236,7 @@
         <v>35</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>36</v>
@@ -4256,24 +4251,24 @@
         <v>56</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>189</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4299,16 +4294,16 @@
         <v>109</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="N22" t="s" s="2">
+      <c r="O22" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>35</v>
@@ -4357,7 +4352,7 @@
         <v>35</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>36</v>
@@ -4372,24 +4367,24 @@
         <v>56</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AM22" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>196</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4415,14 +4410,14 @@
         <v>109</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>35</v>
@@ -4471,7 +4466,7 @@
         <v>35</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>36</v>
@@ -4486,24 +4481,24 @@
         <v>56</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="AL23" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>203</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4529,16 +4524,16 @@
         <v>64</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>35</v>
@@ -4566,10 +4561,10 @@
         <v>125</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>35</v>
@@ -4587,7 +4582,7 @@
         <v>35</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>36</v>
@@ -4602,10 +4597,10 @@
         <v>56</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AL24" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>35</v>
@@ -4616,10 +4611,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4645,10 +4640,10 @@
         <v>131</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4678,11 +4673,11 @@
         <v>136</v>
       </c>
       <c r="Y25" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="Z25" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="Z25" t="s" s="2">
-        <v>215</v>
-      </c>
       <c r="AA25" t="s" s="2">
         <v>35</v>
       </c>
@@ -4699,7 +4694,7 @@
         <v>35</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>36</v>
@@ -4714,10 +4709,10 @@
         <v>56</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>35</v>
@@ -4728,10 +4723,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4840,10 +4835,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4954,10 +4949,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4980,19 +4975,19 @@
         <v>45</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="N28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>35</v>
@@ -5041,7 +5036,7 @@
         <v>35</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>36</v>
@@ -5056,7 +5051,7 @@
         <v>56</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>35</v>
@@ -5070,10 +5065,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5099,16 +5094,16 @@
         <v>109</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>35</v>
@@ -5133,13 +5128,11 @@
         <v>35</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>35</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>35</v>
+        <v>172</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>35</v>
@@ -5157,7 +5150,7 @@
         <v>35</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>36</v>
@@ -5172,24 +5165,24 @@
         <v>56</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="AL29" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AM29" t="s" s="2">
+      <c r="AN29" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>234</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5212,13 +5205,13 @@
         <v>35</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5269,7 +5262,7 @@
         <v>35</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>36</v>
@@ -5284,7 +5277,7 @@
         <v>56</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>35</v>
@@ -5298,10 +5291,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5410,10 +5403,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5524,10 +5517,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5553,10 +5546,10 @@
         <v>64</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5586,43 +5579,43 @@
         <v>125</v>
       </c>
       <c r="Y33" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="Z33" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="Z33" t="s" s="2">
+      <c r="AA33" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF33" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="AA33" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF33" t="s" s="2">
+      <c r="AG33" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="AI33" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="AG33" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="AI33" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>35</v>
@@ -5636,10 +5629,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5665,16 +5658,16 @@
         <v>109</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>35</v>
@@ -5723,7 +5716,7 @@
         <v>35</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>36</v>
@@ -5738,24 +5731,24 @@
         <v>56</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="AL34" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AN34" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>258</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5781,16 +5774,16 @@
         <v>64</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>35</v>
@@ -5818,28 +5811,28 @@
         <v>125</v>
       </c>
       <c r="Y35" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="Z35" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="Z35" t="s" s="2">
+      <c r="AA35" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF35" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>36</v>
@@ -5854,7 +5847,7 @@
         <v>56</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>35</v>
@@ -5868,10 +5861,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5894,16 +5887,16 @@
         <v>45</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5953,7 +5946,7 @@
         <v>35</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>36</v>
@@ -5982,10 +5975,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6011,10 +6004,10 @@
         <v>157</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6065,7 +6058,7 @@
         <v>35</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>36</v>
@@ -6080,7 +6073,7 @@
         <v>56</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>35</v>
@@ -6094,10 +6087,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6120,19 +6113,19 @@
         <v>35</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>35</v>
@@ -6181,7 +6174,7 @@
         <v>35</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>36</v>
@@ -6196,24 +6189,24 @@
         <v>56</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>286</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6322,10 +6315,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6436,10 +6429,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6465,16 +6458,16 @@
         <v>64</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>35</v>
@@ -6487,7 +6480,7 @@
         <v>35</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>35</v>
@@ -6502,28 +6495,28 @@
         <v>125</v>
       </c>
       <c r="Y41" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="Z41" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="Z41" t="s" s="2">
+      <c r="AA41" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF41" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>36</v>
@@ -6538,7 +6531,7 @@
         <v>56</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>35</v>
@@ -6547,15 +6540,15 @@
         <v>35</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6581,13 +6574,13 @@
         <v>64</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6601,7 +6594,7 @@
         <v>35</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>35</v>
@@ -6616,28 +6609,28 @@
         <v>125</v>
       </c>
       <c r="Y42" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="Z42" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="Z42" t="s" s="2">
+      <c r="AA42" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF42" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>36</v>
@@ -6652,7 +6645,7 @@
         <v>56</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>35</v>
@@ -6661,15 +6654,15 @@
         <v>35</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6695,16 +6688,16 @@
         <v>109</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>35</v>
@@ -6717,43 +6710,43 @@
         <v>35</v>
       </c>
       <c r="T43" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF43" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="U43" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V43" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W43" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X43" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>36</v>
@@ -6768,7 +6761,7 @@
         <v>56</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>35</v>
@@ -6782,10 +6775,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6811,10 +6804,10 @@
         <v>109</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6829,43 +6822,43 @@
         <v>35</v>
       </c>
       <c r="T44" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF44" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>36</v>
@@ -6880,28 +6873,28 @@
         <v>56</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="AL44" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AM44" t="s" s="2">
+      <c r="AN44" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>323</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6923,10 +6916,10 @@
         <v>109</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6941,43 +6934,43 @@
         <v>35</v>
       </c>
       <c r="T45" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF45" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="U45" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V45" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W45" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>36</v>
@@ -6992,28 +6985,28 @@
         <v>56</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AL45" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AM45" t="s" s="2">
+      <c r="AN45" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>332</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7035,13 +7028,13 @@
         <v>109</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7055,43 +7048,43 @@
         <v>35</v>
       </c>
       <c r="T46" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF46" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="U46" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X46" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>36</v>
@@ -7106,28 +7099,28 @@
         <v>56</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AL46" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AM46" t="s" s="2">
+      <c r="AN46" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>342</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7149,10 +7142,10 @@
         <v>109</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7182,28 +7175,28 @@
         <v>136</v>
       </c>
       <c r="Y47" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="Z47" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="Z47" t="s" s="2">
+      <c r="AA47" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF47" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>36</v>
@@ -7218,28 +7211,28 @@
         <v>56</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>351</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7261,10 +7254,10 @@
         <v>109</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7279,43 +7272,43 @@
         <v>35</v>
       </c>
       <c r="T48" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF48" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="U48" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V48" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W48" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X48" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z48" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>36</v>
@@ -7330,24 +7323,24 @@
         <v>56</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AL48" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AM48" t="s" s="2">
+      <c r="AN48" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>360</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7373,13 +7366,13 @@
         <v>109</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7429,7 +7422,7 @@
         <v>35</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>36</v>
@@ -7444,24 +7437,24 @@
         <v>56</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>367</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7487,14 +7480,14 @@
         <v>157</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>35</v>
@@ -7507,43 +7500,43 @@
         <v>35</v>
       </c>
       <c r="T50" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF50" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>36</v>
@@ -7558,7 +7551,7 @@
         <v>56</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>35</v>
@@ -7572,10 +7565,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7601,14 +7594,14 @@
         <v>131</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>35</v>
@@ -7633,14 +7626,14 @@
         <v>35</v>
       </c>
       <c r="X51" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="Y51" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="Y51" t="s" s="2">
+      <c r="Z51" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="Z51" t="s" s="2">
-        <v>380</v>
-      </c>
       <c r="AA51" t="s" s="2">
         <v>35</v>
       </c>
@@ -7657,7 +7650,7 @@
         <v>35</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>36</v>
@@ -7672,10 +7665,10 @@
         <v>56</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>35</v>
@@ -7686,10 +7679,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7798,10 +7791,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7912,10 +7905,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7938,19 +7931,19 @@
         <v>45</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>35</v>
@@ -7999,7 +7992,7 @@
         <v>35</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>36</v>
@@ -8014,7 +8007,7 @@
         <v>56</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>35</v>
@@ -8028,10 +8021,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8057,16 +8050,16 @@
         <v>109</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>35</v>
@@ -8115,7 +8108,7 @@
         <v>35</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>36</v>
@@ -8130,24 +8123,24 @@
         <v>56</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AM55" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>387</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8170,17 +8163,17 @@
         <v>35</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>35</v>
@@ -8229,7 +8222,7 @@
         <v>35</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>36</v>
@@ -8244,7 +8237,7 @@
         <v>56</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>35</v>
@@ -8258,10 +8251,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8370,10 +8363,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8484,14 +8477,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8513,10 +8506,10 @@
         <v>90</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>93</v>
@@ -8571,7 +8564,7 @@
         <v>35</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>36</v>
@@ -8600,10 +8593,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8626,13 +8619,13 @@
         <v>35</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8683,7 +8676,7 @@
         <v>35</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>44</v>
@@ -8698,7 +8691,7 @@
         <v>56</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>35</v>
@@ -8712,10 +8705,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8738,13 +8731,13 @@
         <v>35</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8795,7 +8788,7 @@
         <v>35</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>44</v>
@@ -8810,7 +8803,7 @@
         <v>56</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>35</v>
@@ -8824,10 +8817,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8850,13 +8843,13 @@
         <v>35</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8907,7 +8900,7 @@
         <v>35</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>36</v>
@@ -8922,7 +8915,7 @@
         <v>56</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>35</v>
@@ -8936,10 +8929,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8962,19 +8955,19 @@
         <v>45</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="N63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>35</v>
@@ -9023,7 +9016,7 @@
         <v>35</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>36</v>
@@ -9038,7 +9031,7 @@
         <v>56</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>35</v>
@@ -9052,10 +9045,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9164,10 +9157,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9278,10 +9271,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9307,13 +9300,13 @@
         <v>109</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9363,16 +9356,16 @@
         <v>35</v>
       </c>
       <c r="AF66" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="AI66" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>56</v>
@@ -9392,10 +9385,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9421,13 +9414,13 @@
         <v>58</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9456,28 +9449,28 @@
         <v>136</v>
       </c>
       <c r="Y67" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="Z67" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="Z67" t="s" s="2">
+      <c r="AA67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF67" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>36</v>
@@ -9506,10 +9499,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9535,13 +9528,13 @@
         <v>102</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9591,7 +9584,7 @@
         <v>35</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>36</v>
@@ -9606,7 +9599,7 @@
         <v>56</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>35</v>
@@ -9620,10 +9613,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9649,13 +9642,13 @@
         <v>109</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9705,7 +9698,7 @@
         <v>35</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>36</v>
@@ -9729,15 +9722,15 @@
         <v>35</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9760,17 +9753,17 @@
         <v>35</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>35</v>
@@ -9819,7 +9812,7 @@
         <v>35</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>36</v>
@@ -9834,7 +9827,7 @@
         <v>56</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>35</v>
@@ -9848,10 +9841,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9874,16 +9867,16 @@
         <v>35</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -9933,7 +9926,7 @@
         <v>35</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>36</v>
@@ -9948,7 +9941,7 @@
         <v>56</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>35</v>
@@ -9962,10 +9955,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10074,10 +10067,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10188,14 +10181,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10217,10 +10210,10 @@
         <v>90</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>93</v>
@@ -10275,7 +10268,7 @@
         <v>35</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>36</v>
@@ -10304,10 +10297,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10333,10 +10326,10 @@
         <v>64</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10366,11 +10359,11 @@
         <v>125</v>
       </c>
       <c r="Y75" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="Z75" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="Z75" t="s" s="2">
-        <v>464</v>
-      </c>
       <c r="AA75" t="s" s="2">
         <v>35</v>
       </c>
@@ -10387,7 +10380,7 @@
         <v>35</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>36</v>
@@ -10402,7 +10395,7 @@
         <v>56</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>35</v>
@@ -10416,10 +10409,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10442,13 +10435,13 @@
         <v>35</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="L76" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="M76" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10499,7 +10492,7 @@
         <v>35</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>36</v>
@@ -10514,7 +10507,7 @@
         <v>56</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>35</v>
@@ -10528,10 +10521,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10554,13 +10547,13 @@
         <v>35</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="L77" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="L77" t="s" s="2">
+      <c r="M77" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10611,7 +10604,7 @@
         <v>35</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>36</v>
@@ -10626,7 +10619,7 @@
         <v>56</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>35</v>
@@ -10640,10 +10633,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10666,13 +10659,13 @@
         <v>35</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10723,7 +10716,7 @@
         <v>35</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>36</v>
@@ -10738,7 +10731,7 @@
         <v>56</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>35</v>
@@ -10752,10 +10745,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10781,10 +10774,10 @@
         <v>109</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -10835,7 +10828,7 @@
         <v>35</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>36</v>
@@ -10864,10 +10857,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10890,17 +10883,17 @@
         <v>35</v>
       </c>
       <c r="K80" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="L80" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="L80" t="s" s="2">
+      <c r="M80" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>35</v>
@@ -10949,7 +10942,7 @@
         <v>35</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>36</v>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2945" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2945" uniqueCount="525">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,10 +237,10 @@
     <t>Mapping: FiveWs Pattern Mapping</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
     <t/>
@@ -721,10 +721,10 @@
     <t>.name</t>
   </si>
   <si>
+    <t>756: source value from HOSPITAL LOCATION - NAME (#44-.01)</t>
+  </si>
+  <si>
     <t>Dim.Location.LocationName</t>
-  </si>
-  <si>
-    <t>756: source value from HOSPITAL LOCATION - NAME (#44-.01)</t>
   </si>
   <si>
     <t>Location.alias</t>
@@ -743,12 +743,12 @@
 For searching knowing previous names that the location was known by can be very useful.</t>
   </si>
   <si>
+    <t>1277: source value from HOSPITAL LOCATION - SYNONYM (#44-13)</t>
+  </si>
+  <si>
     <t>Dim.Location.LocationAbbreviation</t>
   </si>
   <si>
-    <t>1277: source value from HOSPITAL LOCATION - SYNONYM (#44-13)</t>
-  </si>
-  <si>
     <t>Location.description</t>
   </si>
   <si>
@@ -764,12 +764,12 @@
     <t>.playingEntity[classCode=PLC determinerCode=INSTANCE].desc</t>
   </si>
   <si>
+    <t>1279: source value from HOSPITAL LOCATION - PATIENT FRIENDLY NAME (#44-60)</t>
+  </si>
+  <si>
     <t>Dim.Location.PatientFriendlyLocationName</t>
   </si>
   <si>
-    <t>1279: source value from HOSPITAL LOCATION - PATIENT FRIENDLY NAME (#44-60)</t>
-  </si>
-  <si>
     <t>Location.mode</t>
   </si>
   <si>
@@ -857,10 +857,10 @@
     <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
+    <t>1412: terminologyMaps using VF_LocationStatus on HOSPITAL LOCATION - SERVICE (#44-9)</t>
+  </si>
+  <si>
     <t>Dim.Location.MedicalService</t>
-  </si>
-  <si>
-    <t>1412: terminologyMaps using VF_LocationStatus on HOSPITAL LOCATION - SERVICE (#44-9)</t>
   </si>
   <si>
     <t>Location.telecom</t>
@@ -931,10 +931,10 @@
     <t>./url</t>
   </si>
   <si>
+    <t>1280: transform using concat (44-99," ext. ",44-99.1) on HOSPITAL LOCATION - TELEPHONE &gt; TELEPHONE EXTENSION (#44-99 &gt; 44-99.1)</t>
+  </si>
+  <si>
     <t>Dim.Location.PhoneNumber</t>
-  </si>
-  <si>
-    <t>1280: transform using concat (44-99," ext. ",44-99.1) on HOSPITAL LOCATION - TELEPHONE &gt; TELEPHONE EXTENSION (#44-99 &gt; 44-99.1)</t>
   </si>
   <si>
     <t>Location.telecom.use</t>
@@ -1083,6 +1083,10 @@
     <t>Address.type</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+inv-10:1322: fixed value "physical" {null}</t>
+  </si>
+  <si>
     <t>1328: source not supported case mailing slice</t>
   </si>
   <si>
@@ -1128,10 +1132,10 @@
     <t>AD.part[parttype = AL]</t>
   </si>
   <si>
+    <t>1324: source not supported case mailing slice</t>
+  </si>
+  <si>
     <t>Dim.Institution.StreetAddress2</t>
-  </si>
-  <si>
-    <t>1324: source not supported case mailing slice</t>
   </si>
   <si>
     <t>Location.address.city</t>
@@ -1156,10 +1160,10 @@
     <t>AD.part[parttype = CTY]</t>
   </si>
   <si>
+    <t>1325: source not supported case mailing slice</t>
+  </si>
+  <si>
     <t>Dim.Institution.City</t>
-  </si>
-  <si>
-    <t>1325: source not supported case mailing slice</t>
   </si>
   <si>
     <t>Location.address.district</t>
@@ -1187,10 +1191,10 @@
     <t>AD.part[parttype = CNT | CPA]</t>
   </si>
   <si>
+    <t>1316: source value from HOSPITAL LOCATION - INSTITUTION &gt; DISTRICT (#44-3 &gt; 4-.03)</t>
+  </si>
+  <si>
     <t>Dim.Institution.MedicalDistrict</t>
-  </si>
-  <si>
-    <t>1316: source value from HOSPITAL LOCATION - INSTITUTION &gt; DISTRICT (#44-3 &gt; 4-.03)</t>
   </si>
   <si>
     <t>Location.address.state</t>
@@ -1243,10 +1247,10 @@
     <t>AD.part[parttype = ZIP]</t>
   </si>
   <si>
+    <t>1327: source not supported case mailing slice</t>
+  </si>
+  <si>
     <t>Dim.Institution.Zip</t>
-  </si>
-  <si>
-    <t>1327: source not supported case mailing slice</t>
   </si>
   <si>
     <t>Location.address.country</t>
@@ -1327,10 +1331,10 @@
     <t>Location.physicalType.text</t>
   </si>
   <si>
+    <t>1284: source value from HOSPITAL LOCATION - PHYSICAL LOCATION (#44-10)</t>
+  </si>
+  <si>
     <t>Dim.Location.PhysicalLocation</t>
-  </si>
-  <si>
-    <t>1284: source value from HOSPITAL LOCATION - PHYSICAL LOCATION (#44-10)</t>
   </si>
   <si>
     <t>Location.position</t>
@@ -1512,6 +1516,10 @@
   </si>
   <si>
     <t>Reference.display</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+inv-9:1283: fixed value "Veterans Administration" {null}</t>
   </si>
   <si>
     <t>1283: fixed value = Veterans Administration</t>
@@ -1990,8 +1998,8 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="43.94140625" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="128.8515625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="128.8515625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="43.94140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3938,10 +3946,10 @@
         <v>75</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>75</v>
+        <v>195</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>195</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" hidden="true">
@@ -4274,10 +4282,10 @@
         <v>214</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>75</v>
+        <v>215</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>215</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" hidden="true">
@@ -6438,10 +6446,10 @@
         <v>75</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>75</v>
+        <v>325</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>325</v>
+        <v>75</v>
       </c>
     </row>
     <row r="40" hidden="true">
@@ -6780,10 +6788,10 @@
         <v>75</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>75</v>
+        <v>337</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>337</v>
+        <v>75</v>
       </c>
     </row>
     <row r="43" hidden="true">
@@ -6885,7 +6893,7 @@
         <v>75</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>96</v>
+        <v>346</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>306</v>
@@ -6894,18 +6902,18 @@
         <v>75</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>75</v>
+        <v>347</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>346</v>
+        <v>75</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6931,16 +6939,16 @@
         <v>149</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>75</v>
@@ -6953,7 +6961,7 @@
         <v>75</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>75</v>
@@ -6989,7 +6997,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -7004,7 +7012,7 @@
         <v>96</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>75</v>
@@ -7018,10 +7026,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7047,10 +7055,10 @@
         <v>149</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7065,7 +7073,7 @@
         <v>75</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>75</v>
@@ -7101,7 +7109,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -7116,28 +7124,28 @@
         <v>96</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7159,10 +7167,10 @@
         <v>149</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7177,7 +7185,7 @@
         <v>75</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>75</v>
@@ -7213,7 +7221,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -7228,28 +7236,28 @@
         <v>96</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7271,13 +7279,13 @@
         <v>149</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7291,7 +7299,7 @@
         <v>75</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>75</v>
@@ -7327,7 +7335,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -7342,28 +7350,28 @@
         <v>96</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7385,10 +7393,10 @@
         <v>149</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7418,10 +7426,10 @@
         <v>176</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>75</v>
@@ -7439,7 +7447,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -7454,28 +7462,28 @@
         <v>96</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>75</v>
+        <v>391</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>390</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7497,10 +7505,10 @@
         <v>149</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7515,7 +7523,7 @@
         <v>75</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="U49" t="s" s="2">
         <v>75</v>
@@ -7551,7 +7559,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -7566,24 +7574,24 @@
         <v>96</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7609,13 +7617,13 @@
         <v>149</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7665,7 +7673,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -7680,24 +7688,24 @@
         <v>96</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>75</v>
+        <v>407</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>406</v>
+        <v>75</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7723,14 +7731,14 @@
         <v>197</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>75</v>
@@ -7743,7 +7751,7 @@
         <v>75</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>75</v>
@@ -7779,7 +7787,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -7808,10 +7816,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7837,14 +7845,14 @@
         <v>171</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>75</v>
@@ -7869,13 +7877,13 @@
         <v>75</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>75</v>
@@ -7893,7 +7901,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -7908,7 +7916,7 @@
         <v>96</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>250</v>
@@ -7922,10 +7930,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8034,10 +8042,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8148,10 +8156,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8264,10 +8272,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8372,18 +8380,18 @@
         <v>75</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8406,17 +8414,17 @@
         <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>75</v>
@@ -8465,7 +8473,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -8480,7 +8488,7 @@
         <v>96</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>75</v>
@@ -8494,10 +8502,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8606,10 +8614,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8720,14 +8728,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8749,10 +8757,10 @@
         <v>130</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>133</v>
@@ -8807,7 +8815,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -8836,10 +8844,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8862,13 +8870,13 @@
         <v>75</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8919,7 +8927,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>84</v>
@@ -8934,7 +8942,7 @@
         <v>96</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>75</v>
@@ -8948,10 +8956,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8974,13 +8982,13 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9031,7 +9039,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>84</v>
@@ -9046,7 +9054,7 @@
         <v>96</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>75</v>
@@ -9060,10 +9068,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9086,13 +9094,13 @@
         <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9143,7 +9151,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -9158,7 +9166,7 @@
         <v>96</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>75</v>
@@ -9172,10 +9180,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9198,19 +9206,19 @@
         <v>85</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>75</v>
@@ -9259,7 +9267,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -9274,7 +9282,7 @@
         <v>96</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>75</v>
@@ -9288,10 +9296,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9400,10 +9408,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9514,10 +9522,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9543,13 +9551,13 @@
         <v>149</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9599,7 +9607,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -9608,7 +9616,7 @@
         <v>84</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>96</v>
@@ -9628,10 +9636,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9657,13 +9665,13 @@
         <v>98</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9692,10 +9700,10 @@
         <v>176</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>75</v>
@@ -9713,7 +9721,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -9742,10 +9750,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9771,13 +9779,13 @@
         <v>142</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9827,7 +9835,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -9842,7 +9850,7 @@
         <v>96</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>75</v>
@@ -9856,10 +9864,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9885,13 +9893,13 @@
         <v>149</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9941,7 +9949,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -9953,7 +9961,7 @@
         <v>75</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>96</v>
+        <v>485</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>127</v>
@@ -9962,18 +9970,18 @@
         <v>75</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>75</v>
+        <v>486</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>484</v>
+        <v>75</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9996,17 +10004,17 @@
         <v>75</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>75</v>
@@ -10055,7 +10063,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -10070,7 +10078,7 @@
         <v>96</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>75</v>
@@ -10084,10 +10092,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10110,16 +10118,16 @@
         <v>75</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10169,7 +10177,7 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
@@ -10184,7 +10192,7 @@
         <v>96</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>75</v>
@@ -10198,10 +10206,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10310,10 +10318,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10424,14 +10432,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10453,10 +10461,10 @@
         <v>130</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>133</v>
@@ -10511,7 +10519,7 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
@@ -10540,10 +10548,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10569,10 +10577,10 @@
         <v>104</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10602,10 +10610,10 @@
         <v>165</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>75</v>
@@ -10623,7 +10631,7 @@
         <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -10638,7 +10646,7 @@
         <v>96</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>75</v>
@@ -10652,10 +10660,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10678,13 +10686,13 @@
         <v>75</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10735,7 +10743,7 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
@@ -10750,7 +10758,7 @@
         <v>96</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>75</v>
@@ -10764,10 +10772,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10790,13 +10798,13 @@
         <v>75</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10847,7 +10855,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
@@ -10862,7 +10870,7 @@
         <v>96</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>75</v>
@@ -10876,10 +10884,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10902,13 +10910,13 @@
         <v>75</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -10959,7 +10967,7 @@
         <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
@@ -10974,7 +10982,7 @@
         <v>96</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>75</v>
@@ -10988,10 +10996,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11017,10 +11025,10 @@
         <v>149</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11071,7 +11079,7 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
@@ -11100,10 +11108,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11126,17 +11134,17 @@
         <v>75</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>75</v>
@@ -11185,7 +11193,7 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1084,7 +1084,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-10:1322: fixed value "physical" {null}</t>
+inv-16:1322: fixed value = physical if HOSPITAL LOCATION - INSTITUTION (#44-3) {null}</t>
   </si>
   <si>
     <t>1328: source not supported case mailing slice</t>
@@ -1519,7 +1519,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-9:1283: fixed value "Veterans Administration" {null}</t>
+inv-15:1283: fixed value = Veterans Administration {null}</t>
   </si>
   <si>
     <t>1283: fixed value = Veterans Administration</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1084,7 +1084,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-16:1322: fixed value = physical if HOSPITAL LOCATION - INSTITUTION (#44-3) {null}</t>
+inv-16:1322: fixed value = #physical if HOSPITAL LOCATION - INSTITUTION (#44-3) {null}</t>
   </si>
   <si>
     <t>1328: source not supported case mailing slice</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T19:04:11+00:00</t>
+    <t>2023-12-21T07:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1084,7 +1084,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-16:1322: fixed value = #physical if HOSPITAL LOCATION - INSTITUTION (#44-3) {null}</t>
+inv-17:1322: fixed value = #physical if HOSPITAL LOCATION - INSTITUTION (#44-3) {null}</t>
   </si>
   <si>
     <t>1328: source not supported case mailing slice</t>
@@ -1519,7 +1519,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-15:1283: fixed value = Veterans Administration {null}</t>
+inv-16:1283: fixed value = Veterans Administration {null}</t>
   </si>
   <si>
     <t>1283: fixed value = Veterans Administration</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA HOSPITAL LOCATION (file 44) to FHIR Location</t>
+    <t>This StructureDefinition contains the maps for VistA file HOSPITAL LOCATION (#44) to us-core-location</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1084,7 +1084,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-17:1322: fixed value = #physical if HOSPITAL LOCATION - INSTITUTION (#44-3) {null}</t>
+inv-17:1322: fixed value = #physical when HOSPITAL LOCATION - INSTITUTION (#44-3) {null}</t>
   </si>
   <si>
     <t>1328: source not supported case mailing slice</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2945" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2945" uniqueCount="523">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.13.0</t>
+    <t>0.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-03T19:41:50+00:00</t>
+    <t>2024-01-13T13:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1081,10 +1081,6 @@
   </si>
   <si>
     <t>Address.type</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-17:1322: fixed value = #physical when HOSPITAL LOCATION - INSTITUTION (#44-3) {null}</t>
   </si>
   <si>
     <t>1328: source not supported case mailing slice</t>
@@ -1516,10 +1512,6 @@
   </si>
   <si>
     <t>Reference.display</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-16:1283: fixed value = Veterans Administration {null}</t>
   </si>
   <si>
     <t>1283: fixed value = Veterans Administration</t>
@@ -3857,7 +3849,7 @@
         <v>84</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>75</v>
@@ -4533,7 +4525,7 @@
         <v>77</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>75</v>
@@ -4649,7 +4641,7 @@
         <v>84</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>75</v>
@@ -5333,7 +5325,7 @@
         <v>84</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>75</v>
@@ -5897,7 +5889,7 @@
         <v>84</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>75</v>
@@ -6697,7 +6689,7 @@
         <v>84</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>85</v>
@@ -6813,7 +6805,7 @@
         <v>84</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>75</v>
@@ -6893,7 +6885,7 @@
         <v>75</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>346</v>
+        <v>96</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>306</v>
@@ -6902,7 +6894,7 @@
         <v>75</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>75</v>
@@ -6910,10 +6902,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6939,16 +6931,16 @@
         <v>149</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>75</v>
@@ -6961,43 +6953,43 @@
         <v>75</v>
       </c>
       <c r="T44" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF44" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -7012,7 +7004,7 @@
         <v>96</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>75</v>
@@ -7026,10 +7018,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7055,10 +7047,10 @@
         <v>149</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7073,43 +7065,43 @@
         <v>75</v>
       </c>
       <c r="T45" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF45" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="U45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -7124,28 +7116,28 @@
         <v>96</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="AL45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM45" t="s" s="2">
+      <c r="AN45" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>363</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7167,10 +7159,10 @@
         <v>149</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7185,43 +7177,43 @@
         <v>75</v>
       </c>
       <c r="T46" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF46" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="U46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -7236,28 +7228,28 @@
         <v>96</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="AL46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM46" t="s" s="2">
+      <c r="AN46" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>372</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7267,7 +7259,7 @@
         <v>84</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>75</v>
@@ -7279,13 +7271,13 @@
         <v>149</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7299,43 +7291,43 @@
         <v>75</v>
       </c>
       <c r="T47" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF47" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="U47" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V47" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W47" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X47" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -7350,28 +7342,28 @@
         <v>96</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM47" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="AL47" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM47" t="s" s="2">
+      <c r="AN47" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>382</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7393,10 +7385,10 @@
         <v>149</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7426,28 +7418,28 @@
         <v>176</v>
       </c>
       <c r="Y48" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="Z48" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="Z48" t="s" s="2">
+      <c r="AA48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF48" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -7462,13 +7454,13 @@
         <v>96</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>75</v>
@@ -7476,14 +7468,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7505,10 +7497,10 @@
         <v>149</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7523,43 +7515,43 @@
         <v>75</v>
       </c>
       <c r="T49" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF49" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="U49" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V49" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W49" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X49" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -7574,24 +7566,24 @@
         <v>96</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="AL49" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM49" t="s" s="2">
+      <c r="AN49" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>400</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7605,7 +7597,7 @@
         <v>84</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>75</v>
@@ -7617,13 +7609,13 @@
         <v>149</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7673,7 +7665,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -7688,13 +7680,13 @@
         <v>96</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>75</v>
@@ -7702,10 +7694,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7731,14 +7723,14 @@
         <v>197</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>75</v>
@@ -7751,43 +7743,43 @@
         <v>75</v>
       </c>
       <c r="T51" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF51" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -7816,10 +7808,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7845,14 +7837,14 @@
         <v>171</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>75</v>
@@ -7877,14 +7869,14 @@
         <v>75</v>
       </c>
       <c r="X52" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="Y52" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="Y52" t="s" s="2">
+      <c r="Z52" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="Z52" t="s" s="2">
-        <v>420</v>
-      </c>
       <c r="AA52" t="s" s="2">
         <v>75</v>
       </c>
@@ -7901,7 +7893,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -7916,7 +7908,7 @@
         <v>96</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>250</v>
@@ -7930,10 +7922,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8042,10 +8034,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8156,10 +8148,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8272,10 +8264,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8289,7 +8281,7 @@
         <v>84</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>75</v>
@@ -8380,18 +8372,18 @@
         <v>75</v>
       </c>
       <c r="AM56" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>427</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8414,17 +8406,17 @@
         <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>75</v>
@@ -8473,7 +8465,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -8488,7 +8480,7 @@
         <v>96</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>75</v>
@@ -8502,10 +8494,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8614,10 +8606,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8728,14 +8720,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8757,10 +8749,10 @@
         <v>130</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>133</v>
@@ -8815,7 +8807,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -8844,10 +8836,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8870,13 +8862,13 @@
         <v>75</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8927,7 +8919,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>84</v>
@@ -8942,7 +8934,7 @@
         <v>96</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>75</v>
@@ -8956,10 +8948,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8982,13 +8974,13 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9039,7 +9031,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>84</v>
@@ -9054,7 +9046,7 @@
         <v>96</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>75</v>
@@ -9068,10 +9060,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9094,13 +9086,13 @@
         <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9151,7 +9143,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -9166,7 +9158,7 @@
         <v>96</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>75</v>
@@ -9180,10 +9172,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9206,19 +9198,19 @@
         <v>85</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="N64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>75</v>
@@ -9267,7 +9259,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -9282,7 +9274,7 @@
         <v>96</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>75</v>
@@ -9296,10 +9288,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9408,10 +9400,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9522,10 +9514,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9551,13 +9543,13 @@
         <v>149</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9607,16 +9599,16 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI67" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>96</v>
@@ -9636,10 +9628,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9665,13 +9657,13 @@
         <v>98</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9700,28 +9692,28 @@
         <v>176</v>
       </c>
       <c r="Y68" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="Z68" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="Z68" t="s" s="2">
+      <c r="AA68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF68" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -9750,10 +9742,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9779,13 +9771,13 @@
         <v>142</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9835,7 +9827,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -9850,7 +9842,7 @@
         <v>96</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>75</v>
@@ -9864,10 +9856,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9881,7 +9873,7 @@
         <v>84</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>75</v>
@@ -9893,13 +9885,13 @@
         <v>149</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9949,7 +9941,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -9961,7 +9953,7 @@
         <v>75</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>485</v>
+        <v>96</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>127</v>
@@ -9970,7 +9962,7 @@
         <v>75</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>75</v>
@@ -9978,10 +9970,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10004,17 +9996,17 @@
         <v>75</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>75</v>
@@ -10063,7 +10055,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -10078,7 +10070,7 @@
         <v>96</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>75</v>
@@ -10092,10 +10084,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10118,16 +10110,16 @@
         <v>75</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="N72" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10177,7 +10169,7 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
@@ -10192,7 +10184,7 @@
         <v>96</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>75</v>
@@ -10206,10 +10198,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10318,10 +10310,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10432,14 +10424,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10461,10 +10453,10 @@
         <v>130</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>133</v>
@@ -10519,7 +10511,7 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
@@ -10548,10 +10540,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10577,10 +10569,10 @@
         <v>104</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10610,10 +10602,10 @@
         <v>165</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>75</v>
@@ -10631,7 +10623,7 @@
         <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -10646,7 +10638,7 @@
         <v>96</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>75</v>
@@ -10660,10 +10652,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10686,13 +10678,13 @@
         <v>75</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10743,7 +10735,7 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
@@ -10758,7 +10750,7 @@
         <v>96</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>75</v>
@@ -10772,10 +10764,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10798,13 +10790,13 @@
         <v>75</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10855,7 +10847,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
@@ -10870,7 +10862,7 @@
         <v>96</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>75</v>
@@ -10884,10 +10876,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10910,13 +10902,13 @@
         <v>75</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -10967,7 +10959,7 @@
         <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
@@ -10982,7 +10974,7 @@
         <v>96</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>75</v>
@@ -10996,10 +10988,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11025,10 +11017,10 @@
         <v>149</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11079,7 +11071,7 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
@@ -11108,10 +11100,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11134,17 +11126,17 @@
         <v>75</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>75</v>
@@ -11193,7 +11185,7 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -931,7 +931,7 @@
     <t>./url</t>
   </si>
   <si>
-    <t>1280: transform using concat (44-99," ext. ",44-99.1) on HOSPITAL LOCATION - TELEPHONE &gt; TELEPHONE EXTENSION (#44-99 &gt; 44-99.1)</t>
+    <t>1280: transform using concat (44-99," ext. ",44-99.1) on HOSPITAL LOCATION - TELEPHONE (#44-99)</t>
   </si>
   <si>
     <t>Dim.Location.PhoneNumber</t>
@@ -1187,7 +1187,7 @@
     <t>AD.part[parttype = CNT | CPA]</t>
   </si>
   <si>
-    <t>1316: source value from HOSPITAL LOCATION - INSTITUTION &gt; DISTRICT (#44-3 &gt; 4-.03)</t>
+    <t>1316: source value from HOSPITAL LOCATION - INSTITUTION &gt; INSTITUTION - DISTRICT (#44-3 &gt; 4-.03)</t>
   </si>
   <si>
     <t>Dim.Institution.MedicalDistrict</t>
@@ -1218,7 +1218,7 @@
     <t>AD.part[parttype = STA]</t>
   </si>
   <si>
-    <t>1315: source value from HOSPITAL LOCATION - INSTITUTION &gt; STATE &gt; STATE - ABBREVIATION (#44-3 &gt; 4-.02 &gt; 5-1)</t>
+    <t>1315: source value from HOSPITAL LOCATION - INSTITUTION &gt; INSTITUTION - STATE &gt; STATE - ABBREVIATION (#44-3 &gt; 4-.02 &gt; 5-1)</t>
   </si>
   <si>
     <t>Location.address.postalCode</t>
@@ -1990,7 +1990,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="128.8515625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="123.625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="43.94140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -931,7 +931,7 @@
     <t>./url</t>
   </si>
   <si>
-    <t>1280: transform using concat (44-99," ext. ",44-99.1) on HOSPITAL LOCATION - TELEPHONE (#44-99)</t>
+    <t>1280: transform using concat (44-99," ext. ",44-99.1) on HOSPITAL LOCATION - TELEPHONE &gt; TELEPHONE EXTENSION (#44-99 &gt; 44-99.1)</t>
   </si>
   <si>
     <t>Dim.Location.PhoneNumber</t>
@@ -1187,7 +1187,7 @@
     <t>AD.part[parttype = CNT | CPA]</t>
   </si>
   <si>
-    <t>1316: source value from HOSPITAL LOCATION - INSTITUTION &gt; INSTITUTION - DISTRICT (#44-3 &gt; 4-.03)</t>
+    <t>1316: source value from HOSPITAL LOCATION - INSTITUTION &gt; DISTRICT (#44-3 &gt; 4-.03)</t>
   </si>
   <si>
     <t>Dim.Institution.MedicalDistrict</t>
@@ -1218,7 +1218,7 @@
     <t>AD.part[parttype = STA]</t>
   </si>
   <si>
-    <t>1315: source value from HOSPITAL LOCATION - INSTITUTION &gt; INSTITUTION - STATE &gt; STATE - ABBREVIATION (#44-3 &gt; 4-.02 &gt; 5-1)</t>
+    <t>1315: source value from HOSPITAL LOCATION - INSTITUTION &gt; STATE &gt; STATE - ABBREVIATION (#44-3 &gt; 4-.02 &gt; 5-1)</t>
   </si>
   <si>
     <t>Location.address.postalCode</t>
@@ -1990,7 +1990,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="123.625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="128.8515625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="43.94140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2945" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2945" uniqueCount="521">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1020,9 +1020,6 @@
     <t>.addr</t>
   </si>
   <si>
-    <t>1326: source not supported case mailing slice</t>
-  </si>
-  <si>
     <t>Location.address.id</t>
   </si>
   <si>
@@ -1056,9 +1053,6 @@
     <t>Address.use</t>
   </si>
   <si>
-    <t>1407: source not supported case mailing slice</t>
-  </si>
-  <si>
     <t>Location.address.type</t>
   </si>
   <si>
@@ -1083,7 +1077,7 @@
     <t>Address.type</t>
   </si>
   <si>
-    <t>1328: source not supported case mailing slice</t>
+    <t>1322: fixed value = #physical when HOSPITAL LOCATION - INSTITUTION (#44-3)</t>
   </si>
   <si>
     <t>Location.address.text</t>
@@ -1128,7 +1122,7 @@
     <t>AD.part[parttype = AL]</t>
   </si>
   <si>
-    <t>1324: source not supported case mailing slice</t>
+    <t>1318: source value from HOSPITAL LOCATION - INSTITUTION &gt; STREET ADDR. 2 (#44-3 &gt; 4-1.02)</t>
   </si>
   <si>
     <t>Dim.Institution.StreetAddress2</t>
@@ -1156,7 +1150,7 @@
     <t>AD.part[parttype = CTY]</t>
   </si>
   <si>
-    <t>1325: source not supported case mailing slice</t>
+    <t>1319: source value from HOSPITAL LOCATION - INSTITUTION &gt; CITY (#44-3 &gt; 4-1.03)</t>
   </si>
   <si>
     <t>Dim.Institution.City</t>
@@ -1243,7 +1237,7 @@
     <t>AD.part[parttype = ZIP]</t>
   </si>
   <si>
-    <t>1327: source not supported case mailing slice</t>
+    <t>1320: source value from HOSPITAL LOCATION - INSTITUTION &gt; ZIP (#44-3 &gt; 4-1.04)</t>
   </si>
   <si>
     <t>Dim.Institution.Zip</t>
@@ -1267,7 +1261,7 @@
     <t>AD.part[parttype = CNT]</t>
   </si>
   <si>
-    <t>1406: source not supported case mailing slice</t>
+    <t>1405: source value from HOSPITAL LOCATION - INSTITUTION &gt; COUNTRY &gt; COUNTRY - CODE (#44-3 &gt; 4-801 &gt; 779.004-0.1)</t>
   </si>
   <si>
     <t>Location.address.period</t>
@@ -6438,7 +6432,7 @@
         <v>75</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>325</v>
+        <v>75</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>75</v>
@@ -6446,10 +6440,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6558,10 +6552,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6672,10 +6666,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6689,7 +6683,7 @@
         <v>84</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>85</v>
@@ -6701,16 +6695,16 @@
         <v>104</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>75</v>
@@ -6723,7 +6717,7 @@
         <v>75</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>75</v>
@@ -6738,28 +6732,28 @@
         <v>165</v>
       </c>
       <c r="Y42" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="Z42" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="Z42" t="s" s="2">
+      <c r="AA42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF42" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -6780,7 +6774,7 @@
         <v>75</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>337</v>
+        <v>75</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>75</v>
@@ -6788,10 +6782,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6817,13 +6811,13 @@
         <v>104</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6837,7 +6831,7 @@
         <v>75</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="U43" t="s" s="2">
         <v>75</v>
@@ -6852,28 +6846,28 @@
         <v>165</v>
       </c>
       <c r="Y43" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF43" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -6894,7 +6888,7 @@
         <v>75</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>75</v>
@@ -6902,10 +6896,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6931,16 +6925,16 @@
         <v>149</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>75</v>
@@ -6953,7 +6947,7 @@
         <v>75</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>75</v>
@@ -6989,7 +6983,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -7004,7 +6998,7 @@
         <v>96</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>75</v>
@@ -7018,10 +7012,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7047,10 +7041,10 @@
         <v>149</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7065,7 +7059,7 @@
         <v>75</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>75</v>
@@ -7101,7 +7095,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -7116,28 +7110,28 @@
         <v>96</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>362</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7159,10 +7153,10 @@
         <v>149</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7177,7 +7171,7 @@
         <v>75</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>75</v>
@@ -7213,7 +7207,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -7228,28 +7222,28 @@
         <v>96</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AN46" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>371</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7271,13 +7265,13 @@
         <v>149</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="N47" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7291,7 +7285,7 @@
         <v>75</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>75</v>
@@ -7327,7 +7321,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -7342,28 +7336,28 @@
         <v>96</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>381</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7385,10 +7379,10 @@
         <v>149</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7418,28 +7412,28 @@
         <v>176</v>
       </c>
       <c r="Y48" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF48" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="Z48" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -7454,13 +7448,13 @@
         <v>96</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>75</v>
@@ -7468,14 +7462,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7497,10 +7491,10 @@
         <v>149</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7515,7 +7509,7 @@
         <v>75</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="U49" t="s" s="2">
         <v>75</v>
@@ -7551,7 +7545,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -7566,24 +7560,24 @@
         <v>96</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>399</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7609,13 +7603,13 @@
         <v>149</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7665,7 +7659,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -7680,13 +7674,13 @@
         <v>96</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>75</v>
@@ -7694,10 +7688,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7723,14 +7717,14 @@
         <v>197</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>75</v>
@@ -7743,7 +7737,7 @@
         <v>75</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>75</v>
@@ -7779,7 +7773,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -7808,10 +7802,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7837,14 +7831,14 @@
         <v>171</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>75</v>
@@ -7869,14 +7863,14 @@
         <v>75</v>
       </c>
       <c r="X52" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="Z52" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="Y52" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>419</v>
-      </c>
       <c r="AA52" t="s" s="2">
         <v>75</v>
       </c>
@@ -7893,7 +7887,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -7908,7 +7902,7 @@
         <v>96</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>250</v>
@@ -7922,10 +7916,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8034,10 +8028,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8148,10 +8142,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8264,10 +8258,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8372,18 +8366,18 @@
         <v>75</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8406,17 +8400,17 @@
         <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>75</v>
@@ -8465,7 +8459,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -8480,7 +8474,7 @@
         <v>96</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>75</v>
@@ -8494,10 +8488,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8606,10 +8600,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8720,14 +8714,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8749,10 +8743,10 @@
         <v>130</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>133</v>
@@ -8807,7 +8801,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -8836,10 +8830,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8862,13 +8856,13 @@
         <v>75</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8919,7 +8913,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>84</v>
@@ -8934,7 +8928,7 @@
         <v>96</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>75</v>
@@ -8948,10 +8942,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8974,13 +8968,13 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9031,7 +9025,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>84</v>
@@ -9046,7 +9040,7 @@
         <v>96</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>75</v>
@@ -9060,10 +9054,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9086,13 +9080,13 @@
         <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9143,7 +9137,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -9158,7 +9152,7 @@
         <v>96</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>75</v>
@@ -9172,10 +9166,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9198,19 +9192,19 @@
         <v>85</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>75</v>
@@ -9259,7 +9253,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -9274,7 +9268,7 @@
         <v>96</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>75</v>
@@ -9288,10 +9282,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9400,10 +9394,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9514,10 +9508,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9543,13 +9537,13 @@
         <v>149</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9599,7 +9593,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -9608,7 +9602,7 @@
         <v>84</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>96</v>
@@ -9628,10 +9622,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9657,13 +9651,13 @@
         <v>98</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="N68" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9692,28 +9686,28 @@
         <v>176</v>
       </c>
       <c r="Y68" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF68" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -9742,10 +9736,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9771,13 +9765,13 @@
         <v>142</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="N69" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9827,7 +9821,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -9842,7 +9836,7 @@
         <v>96</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>75</v>
@@ -9856,10 +9850,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9885,13 +9879,13 @@
         <v>149</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="N70" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9941,7 +9935,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -9962,7 +9956,7 @@
         <v>75</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>75</v>
@@ -9970,10 +9964,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9996,17 +9990,17 @@
         <v>75</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>75</v>
@@ -10055,7 +10049,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -10070,7 +10064,7 @@
         <v>96</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>75</v>
@@ -10084,10 +10078,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10110,16 +10104,16 @@
         <v>75</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="N72" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10169,7 +10163,7 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
@@ -10184,7 +10178,7 @@
         <v>96</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>75</v>
@@ -10198,10 +10192,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10310,10 +10304,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10424,14 +10418,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10453,10 +10447,10 @@
         <v>130</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>133</v>
@@ -10511,7 +10505,7 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
@@ -10540,10 +10534,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10569,10 +10563,10 @@
         <v>104</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10602,10 +10596,10 @@
         <v>165</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>75</v>
@@ -10623,7 +10617,7 @@
         <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -10638,7 +10632,7 @@
         <v>96</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>75</v>
@@ -10652,10 +10646,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10678,13 +10672,13 @@
         <v>75</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10735,7 +10729,7 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
@@ -10750,7 +10744,7 @@
         <v>96</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>75</v>
@@ -10764,10 +10758,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10790,13 +10784,13 @@
         <v>75</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10847,7 +10841,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
@@ -10862,7 +10856,7 @@
         <v>96</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>75</v>
@@ -10876,10 +10870,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10902,13 +10896,13 @@
         <v>75</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -10959,7 +10953,7 @@
         <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
@@ -10974,7 +10968,7 @@
         <v>96</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>75</v>
@@ -10988,10 +10982,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11017,10 +11011,10 @@
         <v>149</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11071,7 +11065,7 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
@@ -11100,10 +11094,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11126,17 +11120,17 @@
         <v>75</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>521</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>75</v>
@@ -11185,7 +11179,7 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2945" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2945" uniqueCount="523">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1063,6 +1063,9 @@
   </si>
   <si>
     <t>The definition of Address states that "address is intended to describe postal addresses, not physical locations". However, many applications track whether an address has a dual purpose of being a location that can be visited as well as being a valid delivery destination, and Postal addresses are often used as proxies for physical locations (also see the [Location](http://hl7.org/fhir/R4/location.html#) resource).</t>
+  </si>
+  <si>
+    <t>physical</t>
   </si>
   <si>
     <t>both</t>
@@ -1503,6 +1506,9 @@
   </si>
   <si>
     <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
+  </si>
+  <si>
+    <t>Veterans Administration</t>
   </si>
   <si>
     <t>Reference.display</t>
@@ -6828,10 +6834,10 @@
         <v>75</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>75</v>
+        <v>340</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="U43" t="s" s="2">
         <v>75</v>
@@ -6846,10 +6852,10 @@
         <v>165</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>75</v>
@@ -6867,7 +6873,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -6888,7 +6894,7 @@
         <v>75</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>75</v>
@@ -6896,10 +6902,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6925,16 +6931,16 @@
         <v>149</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>75</v>
@@ -6947,7 +6953,7 @@
         <v>75</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>75</v>
@@ -6983,7 +6989,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -6998,7 +7004,7 @@
         <v>96</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>75</v>
@@ -7012,10 +7018,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7041,10 +7047,10 @@
         <v>149</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7059,7 +7065,7 @@
         <v>75</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>75</v>
@@ -7095,7 +7101,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -7110,28 +7116,28 @@
         <v>96</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7153,10 +7159,10 @@
         <v>149</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7171,7 +7177,7 @@
         <v>75</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>75</v>
@@ -7207,7 +7213,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -7222,28 +7228,28 @@
         <v>96</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7265,13 +7271,13 @@
         <v>149</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7285,7 +7291,7 @@
         <v>75</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>75</v>
@@ -7321,7 +7327,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -7336,28 +7342,28 @@
         <v>96</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7379,10 +7385,10 @@
         <v>149</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7412,10 +7418,10 @@
         <v>176</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>75</v>
@@ -7433,7 +7439,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -7448,13 +7454,13 @@
         <v>96</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>75</v>
@@ -7462,14 +7468,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7491,10 +7497,10 @@
         <v>149</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7509,7 +7515,7 @@
         <v>75</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="U49" t="s" s="2">
         <v>75</v>
@@ -7545,7 +7551,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -7560,24 +7566,24 @@
         <v>96</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7603,13 +7609,13 @@
         <v>149</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7659,7 +7665,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -7674,13 +7680,13 @@
         <v>96</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>75</v>
@@ -7688,10 +7694,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7717,14 +7723,14 @@
         <v>197</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>75</v>
@@ -7737,7 +7743,7 @@
         <v>75</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>75</v>
@@ -7773,7 +7779,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -7802,10 +7808,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7831,14 +7837,14 @@
         <v>171</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>75</v>
@@ -7863,13 +7869,13 @@
         <v>75</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>75</v>
@@ -7887,7 +7893,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -7902,7 +7908,7 @@
         <v>96</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>250</v>
@@ -7916,10 +7922,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8028,10 +8034,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8142,10 +8148,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8258,10 +8264,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8366,18 +8372,18 @@
         <v>75</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8400,17 +8406,17 @@
         <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>75</v>
@@ -8459,7 +8465,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -8474,7 +8480,7 @@
         <v>96</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>75</v>
@@ -8488,10 +8494,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8600,10 +8606,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8714,14 +8720,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8743,10 +8749,10 @@
         <v>130</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>133</v>
@@ -8801,7 +8807,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -8830,10 +8836,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8856,13 +8862,13 @@
         <v>75</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8913,7 +8919,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>84</v>
@@ -8928,7 +8934,7 @@
         <v>96</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>75</v>
@@ -8942,10 +8948,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8968,13 +8974,13 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9025,7 +9031,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>84</v>
@@ -9040,7 +9046,7 @@
         <v>96</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>75</v>
@@ -9054,10 +9060,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9080,13 +9086,13 @@
         <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9137,7 +9143,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -9152,7 +9158,7 @@
         <v>96</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>75</v>
@@ -9166,10 +9172,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9192,19 +9198,19 @@
         <v>85</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>75</v>
@@ -9253,7 +9259,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -9268,7 +9274,7 @@
         <v>96</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>75</v>
@@ -9282,10 +9288,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9394,10 +9400,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9508,10 +9514,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9537,13 +9543,13 @@
         <v>149</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9593,7 +9599,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -9602,7 +9608,7 @@
         <v>84</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>96</v>
@@ -9622,10 +9628,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9651,13 +9657,13 @@
         <v>98</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9686,10 +9692,10 @@
         <v>176</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>75</v>
@@ -9707,7 +9713,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -9736,10 +9742,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9765,13 +9771,13 @@
         <v>142</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9821,7 +9827,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -9836,7 +9842,7 @@
         <v>96</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>75</v>
@@ -9850,10 +9856,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9879,13 +9885,13 @@
         <v>149</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9896,7 +9902,7 @@
         <v>75</v>
       </c>
       <c r="S70" t="s" s="2">
-        <v>75</v>
+        <v>482</v>
       </c>
       <c r="T70" t="s" s="2">
         <v>75</v>
@@ -9935,7 +9941,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -9956,7 +9962,7 @@
         <v>75</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>75</v>
@@ -9964,10 +9970,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9990,17 +9996,17 @@
         <v>75</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>75</v>
@@ -10049,7 +10055,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -10064,7 +10070,7 @@
         <v>96</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>75</v>
@@ -10078,10 +10084,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10104,16 +10110,16 @@
         <v>75</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10163,7 +10169,7 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
@@ -10178,7 +10184,7 @@
         <v>96</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>75</v>
@@ -10192,10 +10198,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10304,10 +10310,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10418,14 +10424,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10447,10 +10453,10 @@
         <v>130</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>133</v>
@@ -10505,7 +10511,7 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
@@ -10534,10 +10540,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10563,10 +10569,10 @@
         <v>104</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10596,10 +10602,10 @@
         <v>165</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>75</v>
@@ -10617,7 +10623,7 @@
         <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -10632,7 +10638,7 @@
         <v>96</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>75</v>
@@ -10646,10 +10652,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10672,13 +10678,13 @@
         <v>75</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10729,7 +10735,7 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
@@ -10744,7 +10750,7 @@
         <v>96</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>75</v>
@@ -10758,10 +10764,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10784,13 +10790,13 @@
         <v>75</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10841,7 +10847,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
@@ -10856,7 +10862,7 @@
         <v>96</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>75</v>
@@ -10870,10 +10876,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10896,13 +10902,13 @@
         <v>75</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -10953,7 +10959,7 @@
         <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
@@ -10968,7 +10974,7 @@
         <v>96</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>75</v>
@@ -10982,10 +10988,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11011,10 +11017,10 @@
         <v>149</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11065,7 +11071,7 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
@@ -11094,10 +11100,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11120,17 +11126,17 @@
         <v>75</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>75</v>
@@ -11179,7 +11185,7 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -934,7 +934,8 @@
     <t>1280: transform using concat (44-99," ext. ",44-99.1) on HOSPITAL LOCATION - TELEPHONE &gt; TELEPHONE EXTENSION (#44-99 &gt; 44-99.1)</t>
   </si>
   <si>
-    <t>Dim.Location.PhoneNumber</t>
+    <t>Dim.Location.PhoneNumber
+Dim.Location.PhoneNumberExtension</t>
   </si>
   <si>
     <t>Location.telecom.use</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -231,16 +231,16 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
     <t>Mapping: RIM Mapping</t>
   </si>
   <si>
     <t>Mapping: FiveWs Pattern Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
     <t/>
@@ -619,10 +619,10 @@
     <t>Identifier.value</t>
   </si>
   <si>
+    <t>755: source value from HOSPITAL LOCATION - IEN (#44-.001)</t>
+  </si>
+  <si>
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
-  </si>
-  <si>
-    <t>755: source value from HOSPITAL LOCATION - IEN (#44-.001)</t>
   </si>
   <si>
     <t>Location.identifier.period</t>
@@ -678,13 +678,13 @@
     <t>http://va.gov/fhir/ValueSet/VSVFLocationStatus</t>
   </si>
   <si>
+    <t>1278: terminologyMaps using VF_LocationStatus</t>
+  </si>
+  <si>
     <t>.statusCode</t>
   </si>
   <si>
     <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>1278: terminologyMaps using VF_LocationStatus</t>
   </si>
   <si>
     <t>Location.operationalStatus</t>
@@ -718,13 +718,13 @@
     <t>If the name of a location changes, consider putting the old name in the alias column so that it can still be located through searches.</t>
   </si>
   <si>
+    <t>756: source value from HOSPITAL LOCATION - NAME (#44-.01)</t>
+  </si>
+  <si>
+    <t>Dim.Location.LocationName</t>
+  </si>
+  <si>
     <t>.name</t>
-  </si>
-  <si>
-    <t>756: source value from HOSPITAL LOCATION - NAME (#44-.01)</t>
-  </si>
-  <si>
-    <t>Dim.Location.LocationName</t>
   </si>
   <si>
     <t>Location.alias</t>
@@ -761,15 +761,15 @@
     <t>Humans need additional information to verify a correct location has been identified.</t>
   </si>
   <si>
+    <t>1279: source value from HOSPITAL LOCATION - PATIENT FRIENDLY NAME (#44-60)</t>
+  </si>
+  <si>
+    <t>Dim.Location.PatientFriendlyLocationName</t>
+  </si>
+  <si>
     <t>.playingEntity[classCode=PLC determinerCode=INSTANCE].desc</t>
   </si>
   <si>
-    <t>1279: source value from HOSPITAL LOCATION - PATIENT FRIENDLY NAME (#44-60)</t>
-  </si>
-  <si>
-    <t>Dim.Location.PatientFriendlyLocationName</t>
-  </si>
-  <si>
     <t>Location.mode</t>
   </si>
   <si>
@@ -854,13 +854,13 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
+    <t>1412: terminologyMaps using VF_LocationStatus on HOSPITAL LOCATION - SERVICE (#44-9)</t>
+  </si>
+  <si>
+    <t>Dim.Location.MedicalService</t>
+  </si>
+  <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>1412: terminologyMaps using VF_LocationStatus on HOSPITAL LOCATION - SERVICE (#44-9)</t>
-  </si>
-  <si>
-    <t>Dim.Location.MedicalService</t>
   </si>
   <si>
     <t>Location.telecom</t>
@@ -928,9 +928,6 @@
     <t>ContactPoint.value</t>
   </si>
   <si>
-    <t>./url</t>
-  </si>
-  <si>
     <t>1280: transform using concat (44-99," ext. ",44-99.1) on HOSPITAL LOCATION - TELEPHONE &gt; TELEPHONE EXTENSION (#44-99 &gt; 44-99.1)</t>
   </si>
   <si>
@@ -938,6 +935,9 @@
 Dim.Location.PhoneNumberExtension</t>
   </si>
   <si>
+    <t>./url</t>
+  </si>
+  <si>
     <t>Location.telecom.use</t>
   </si>
   <si>
@@ -1123,13 +1123,13 @@
     <t>Address.line</t>
   </si>
   <si>
+    <t>1318: source value from HOSPITAL LOCATION - INSTITUTION &gt; STREET ADDR. 2 (#44-3 &gt; 4-1.02)</t>
+  </si>
+  <si>
+    <t>Dim.Institution.StreetAddress2</t>
+  </si>
+  <si>
     <t>AD.part[parttype = AL]</t>
-  </si>
-  <si>
-    <t>1318: source value from HOSPITAL LOCATION - INSTITUTION &gt; STREET ADDR. 2 (#44-3 &gt; 4-1.02)</t>
-  </si>
-  <si>
-    <t>Dim.Institution.StreetAddress2</t>
   </si>
   <si>
     <t>Location.address.city</t>
@@ -1151,13 +1151,13 @@
     <t>Address.city</t>
   </si>
   <si>
+    <t>1319: source value from HOSPITAL LOCATION - INSTITUTION &gt; CITY (#44-3 &gt; 4-1.03)</t>
+  </si>
+  <si>
+    <t>Dim.Institution.City</t>
+  </si>
+  <si>
     <t>AD.part[parttype = CTY]</t>
-  </si>
-  <si>
-    <t>1319: source value from HOSPITAL LOCATION - INSTITUTION &gt; CITY (#44-3 &gt; 4-1.03)</t>
-  </si>
-  <si>
-    <t>Dim.Institution.City</t>
   </si>
   <si>
     <t>Location.address.district</t>
@@ -1182,13 +1182,13 @@
     <t>Address.district</t>
   </si>
   <si>
+    <t>1316: source value from HOSPITAL LOCATION - INSTITUTION &gt; DISTRICT (#44-3 &gt; 4-.03)</t>
+  </si>
+  <si>
+    <t>Dim.Institution.MedicalDistrict</t>
+  </si>
+  <si>
     <t>AD.part[parttype = CNT | CPA]</t>
-  </si>
-  <si>
-    <t>1316: source value from HOSPITAL LOCATION - INSTITUTION &gt; DISTRICT (#44-3 &gt; 4-.03)</t>
-  </si>
-  <si>
-    <t>Dim.Institution.MedicalDistrict</t>
   </si>
   <si>
     <t>Location.address.state</t>
@@ -1213,10 +1213,10 @@
     <t>Address.state</t>
   </si>
   <si>
+    <t>1315: source value from HOSPITAL LOCATION - INSTITUTION &gt; STATE &gt; STATE - ABBREVIATION (#44-3 &gt; 4-.02 &gt; 5-1)</t>
+  </si>
+  <si>
     <t>AD.part[parttype = STA]</t>
-  </si>
-  <si>
-    <t>1315: source value from HOSPITAL LOCATION - INSTITUTION &gt; STATE &gt; STATE - ABBREVIATION (#44-3 &gt; 4-.02 &gt; 5-1)</t>
   </si>
   <si>
     <t>Location.address.postalCode</t>
@@ -1238,15 +1238,15 @@
     <t>Address.postalCode</t>
   </si>
   <si>
+    <t>1320: source value from HOSPITAL LOCATION - INSTITUTION &gt; ZIP (#44-3 &gt; 4-1.04)</t>
+  </si>
+  <si>
+    <t>Dim.Institution.Zip</t>
+  </si>
+  <si>
     <t>AD.part[parttype = ZIP]</t>
   </si>
   <si>
-    <t>1320: source value from HOSPITAL LOCATION - INSTITUTION &gt; ZIP (#44-3 &gt; 4-1.04)</t>
-  </si>
-  <si>
-    <t>Dim.Institution.Zip</t>
-  </si>
-  <si>
     <t>Location.address.country</t>
   </si>
   <si>
@@ -1262,10 +1262,10 @@
     <t>Address.country</t>
   </si>
   <si>
+    <t>1405: source value from HOSPITAL LOCATION - INSTITUTION &gt; COUNTRY &gt; COUNTRY - CODE (#44-3 &gt; 4-801 &gt; 779.004-0.1)</t>
+  </si>
+  <si>
     <t>AD.part[parttype = CNT]</t>
-  </si>
-  <si>
-    <t>1405: source value from HOSPITAL LOCATION - INSTITUTION &gt; COUNTRY &gt; COUNTRY - CODE (#44-3 &gt; 4-801 &gt; 779.004-0.1)</t>
   </si>
   <si>
     <t>Location.address.period</t>
@@ -1989,10 +1989,10 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="102.6171875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="128.8515625" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="128.8515625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="102.6171875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2219,13 +2219,13 @@
         <v>81</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="AL2" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM2" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN2" t="s" s="2">
         <v>75</v>
@@ -2787,13 +2787,13 @@
         <v>96</v>
       </c>
       <c r="AK7" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL7" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM7" t="s" s="2">
         <v>119</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>75</v>
@@ -2901,13 +2901,13 @@
         <v>75</v>
       </c>
       <c r="AK8" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL8" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM8" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="AL8" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM8" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>75</v>
@@ -3015,13 +3015,13 @@
         <v>135</v>
       </c>
       <c r="AK9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM9" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="AL9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM9" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>75</v>
@@ -3131,13 +3131,13 @@
         <v>135</v>
       </c>
       <c r="AK10" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL10" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM10" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="AL10" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM10" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>75</v>
@@ -3245,16 +3245,16 @@
         <v>96</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="AM11" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AN11" t="s" s="2">
-        <v>75</v>
       </c>
     </row>
     <row r="12" hidden="true">
@@ -3357,13 +3357,13 @@
         <v>75</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM12" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>75</v>
@@ -3471,13 +3471,13 @@
         <v>135</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>75</v>
@@ -3587,13 +3587,13 @@
         <v>96</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>75</v>
@@ -3703,13 +3703,13 @@
         <v>96</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM15" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>75</v>
@@ -3819,13 +3819,13 @@
         <v>96</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM16" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM16" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>75</v>
@@ -4045,13 +4045,13 @@
         <v>96</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>75</v>
@@ -4159,13 +4159,13 @@
         <v>96</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>75</v>
@@ -4272,13 +4272,13 @@
         <v>213</v>
       </c>
       <c r="AL20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>75</v>
       </c>
     </row>
     <row r="21" hidden="true">
@@ -4381,16 +4381,16 @@
         <v>96</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="AN21" t="s" s="2">
-        <v>75</v>
+        <v>215</v>
       </c>
     </row>
     <row r="22" hidden="true">
@@ -4498,13 +4498,13 @@
         <v>226</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>75</v>
+        <v>227</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>228</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" hidden="true">
@@ -4611,16 +4611,16 @@
         <v>96</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>75</v>
+        <v>235</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>235</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" hidden="true">
@@ -4728,13 +4728,13 @@
         <v>240</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>75</v>
+        <v>241</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>242</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" hidden="true">
@@ -4841,16 +4841,16 @@
         <v>96</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>75</v>
       </c>
     </row>
     <row r="26" hidden="true">
@@ -4953,16 +4953,16 @@
         <v>96</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="AL26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>75</v>
       </c>
     </row>
     <row r="27" hidden="true">
@@ -5065,13 +5065,13 @@
         <v>75</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>75</v>
@@ -5179,13 +5179,13 @@
         <v>135</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>75</v>
@@ -5295,13 +5295,13 @@
         <v>96</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>75</v>
@@ -5412,13 +5412,13 @@
         <v>271</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>75</v>
+        <v>272</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>273</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" hidden="true">
@@ -5521,13 +5521,13 @@
         <v>96</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>75</v>
@@ -5633,13 +5633,13 @@
         <v>75</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>75</v>
@@ -5747,13 +5747,13 @@
         <v>135</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>75</v>
@@ -5859,13 +5859,13 @@
         <v>96</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>75</v>
@@ -5978,13 +5978,13 @@
         <v>295</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>75</v>
+        <v>296</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>297</v>
+        <v>75</v>
       </c>
     </row>
     <row r="36" hidden="true">
@@ -6091,13 +6091,13 @@
         <v>96</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM36" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>75</v>
@@ -6205,13 +6205,13 @@
         <v>96</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>75</v>
@@ -6317,13 +6317,13 @@
         <v>96</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>75</v>
@@ -6433,13 +6433,13 @@
         <v>96</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>75</v>
@@ -6545,13 +6545,13 @@
         <v>75</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>75</v>
@@ -6659,13 +6659,13 @@
         <v>135</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>75</v>
@@ -6775,13 +6775,13 @@
         <v>96</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>75</v>
@@ -6889,13 +6889,13 @@
         <v>96</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>75</v>
@@ -7005,13 +7005,13 @@
         <v>96</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>75</v>
@@ -7120,13 +7120,13 @@
         <v>359</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>75</v>
+        <v>360</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>361</v>
+        <v>75</v>
       </c>
     </row>
     <row r="46" hidden="true">
@@ -7232,13 +7232,13 @@
         <v>368</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>75</v>
+        <v>369</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>370</v>
+        <v>75</v>
       </c>
     </row>
     <row r="47" hidden="true">
@@ -7346,13 +7346,13 @@
         <v>378</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>75</v>
+        <v>379</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>380</v>
+        <v>75</v>
       </c>
     </row>
     <row r="48" hidden="true">
@@ -7570,13 +7570,13 @@
         <v>396</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>75</v>
+        <v>397</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>398</v>
+        <v>75</v>
       </c>
     </row>
     <row r="50" hidden="true">
@@ -7795,13 +7795,13 @@
         <v>96</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>75</v>
@@ -7909,16 +7909,16 @@
         <v>96</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="AL52" t="s" s="2">
+      <c r="AN52" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>75</v>
       </c>
     </row>
     <row r="53" hidden="true">
@@ -8021,13 +8021,13 @@
         <v>75</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>75</v>
@@ -8135,13 +8135,13 @@
         <v>135</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>75</v>
@@ -8251,13 +8251,13 @@
         <v>96</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>75</v>
@@ -8367,16 +8367,16 @@
         <v>96</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>271</v>
+        <v>424</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>75</v>
+        <v>425</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>424</v>
+        <v>273</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>425</v>
+        <v>75</v>
       </c>
     </row>
     <row r="57" hidden="true">
@@ -8481,13 +8481,13 @@
         <v>96</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>75</v>
@@ -8593,13 +8593,13 @@
         <v>75</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>75</v>
@@ -8707,13 +8707,13 @@
         <v>135</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>75</v>
@@ -8823,13 +8823,13 @@
         <v>135</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM60" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>75</v>
@@ -8935,13 +8935,13 @@
         <v>96</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM61" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>75</v>
@@ -9047,13 +9047,13 @@
         <v>96</v>
       </c>
       <c r="AK62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM62" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>75</v>
@@ -9159,13 +9159,13 @@
         <v>96</v>
       </c>
       <c r="AK63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM63" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>75</v>
@@ -9275,13 +9275,13 @@
         <v>96</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM64" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>75</v>
@@ -9387,13 +9387,13 @@
         <v>75</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM65" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>75</v>
@@ -9501,13 +9501,13 @@
         <v>135</v>
       </c>
       <c r="AK66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM66" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>75</v>
@@ -9615,13 +9615,13 @@
         <v>96</v>
       </c>
       <c r="AK67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM67" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>75</v>
@@ -9729,13 +9729,13 @@
         <v>96</v>
       </c>
       <c r="AK68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM68" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>75</v>
@@ -9843,13 +9843,13 @@
         <v>96</v>
       </c>
       <c r="AK69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM69" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>75</v>
@@ -9957,13 +9957,13 @@
         <v>96</v>
       </c>
       <c r="AK70" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM70" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>484</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>75</v>
@@ -10071,13 +10071,13 @@
         <v>96</v>
       </c>
       <c r="AK71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM71" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>75</v>
@@ -10185,13 +10185,13 @@
         <v>96</v>
       </c>
       <c r="AK72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM72" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>75</v>
@@ -10297,13 +10297,13 @@
         <v>75</v>
       </c>
       <c r="AK73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM73" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>75</v>
@@ -10411,13 +10411,13 @@
         <v>135</v>
       </c>
       <c r="AK74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM74" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>75</v>
@@ -10527,13 +10527,13 @@
         <v>135</v>
       </c>
       <c r="AK75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM75" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>75</v>
@@ -10639,13 +10639,13 @@
         <v>96</v>
       </c>
       <c r="AK76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM76" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>75</v>
@@ -10751,13 +10751,13 @@
         <v>96</v>
       </c>
       <c r="AK77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM77" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>75</v>
@@ -10863,13 +10863,13 @@
         <v>96</v>
       </c>
       <c r="AK78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM78" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>75</v>
@@ -10975,13 +10975,13 @@
         <v>96</v>
       </c>
       <c r="AK79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM79" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>75</v>
@@ -11087,13 +11087,13 @@
         <v>96</v>
       </c>
       <c r="AK80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM80" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>75</v>
@@ -11201,13 +11201,13 @@
         <v>96</v>
       </c>
       <c r="AK81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM81" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>75</v>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file HOSPITAL LOCATION (#44) to us-core-location</t>
+    <t>This StructureDefinition contains the maps for VistA file HOSPITAL LOCATION (44) to us-core-location</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -619,7 +619,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>755: source value from HOSPITAL LOCATION - IEN (#44-.001)</t>
+    <t>755: source value from HOSPITAL LOCATION - IEN (44-.001)</t>
   </si>
   <si>
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
@@ -718,7 +718,7 @@
     <t>If the name of a location changes, consider putting the old name in the alias column so that it can still be located through searches.</t>
   </si>
   <si>
-    <t>756: source value from HOSPITAL LOCATION - NAME (#44-.01)</t>
+    <t>756: source value from HOSPITAL LOCATION - NAME (44-.01)</t>
   </si>
   <si>
     <t>Dim.Location.LocationName</t>
@@ -743,7 +743,7 @@
 For searching knowing previous names that the location was known by can be very useful.</t>
   </si>
   <si>
-    <t>1277: source value from HOSPITAL LOCATION - SYNONYM (#44-13)</t>
+    <t>1277: source value from HOSPITAL LOCATION - SYNONYM (44-13)</t>
   </si>
   <si>
     <t>Dim.Location.LocationAbbreviation</t>
@@ -761,7 +761,7 @@
     <t>Humans need additional information to verify a correct location has been identified.</t>
   </si>
   <si>
-    <t>1279: source value from HOSPITAL LOCATION - PATIENT FRIENDLY NAME (#44-60)</t>
+    <t>1279: source value from HOSPITAL LOCATION - PATIENT FRIENDLY NAME (44-60)</t>
   </si>
   <si>
     <t>Dim.Location.PatientFriendlyLocationName</t>
@@ -854,7 +854,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1412: terminologyMaps using VF_LocationStatus on HOSPITAL LOCATION - SERVICE (#44-9)</t>
+    <t>1412: terminologyMaps using VF_LocationStatus on HOSPITAL LOCATION - SERVICE (44-9)</t>
   </si>
   <si>
     <t>Dim.Location.MedicalService</t>
@@ -928,7 +928,7 @@
     <t>ContactPoint.value</t>
   </si>
   <si>
-    <t>1280: transform using concat (44-99," ext. ",44-99.1) on HOSPITAL LOCATION - TELEPHONE &gt; TELEPHONE EXTENSION (#44-99 &gt; 44-99.1)</t>
+    <t>1280: transform using concat (44-99," ext. ",44-99.1) on HOSPITAL LOCATION - TELEPHONE &gt; TELEPHONE EXTENSION (44-99 &gt; 44-99.1)</t>
   </si>
   <si>
     <t>Dim.Location.PhoneNumber
@@ -1081,7 +1081,7 @@
     <t>Address.type</t>
   </si>
   <si>
-    <t>1322: fixed value = #physical when HOSPITAL LOCATION - INSTITUTION (#44-3)</t>
+    <t>1322: fixed value = #physical when HOSPITAL LOCATION - INSTITUTION (44-3)</t>
   </si>
   <si>
     <t>Location.address.text</t>
@@ -1123,7 +1123,7 @@
     <t>Address.line</t>
   </si>
   <si>
-    <t>1318: source value from HOSPITAL LOCATION - INSTITUTION &gt; STREET ADDR. 2 (#44-3 &gt; 4-1.02)</t>
+    <t>1318: source value from HOSPITAL LOCATION - INSTITUTION &gt; STREET ADDR. 2 (44-3 &gt; 4-1.02)</t>
   </si>
   <si>
     <t>Dim.Institution.StreetAddress2</t>
@@ -1151,7 +1151,7 @@
     <t>Address.city</t>
   </si>
   <si>
-    <t>1319: source value from HOSPITAL LOCATION - INSTITUTION &gt; CITY (#44-3 &gt; 4-1.03)</t>
+    <t>1319: source value from HOSPITAL LOCATION - INSTITUTION &gt; CITY (44-3 &gt; 4-1.03)</t>
   </si>
   <si>
     <t>Dim.Institution.City</t>
@@ -1182,7 +1182,7 @@
     <t>Address.district</t>
   </si>
   <si>
-    <t>1316: source value from HOSPITAL LOCATION - INSTITUTION &gt; DISTRICT (#44-3 &gt; 4-.03)</t>
+    <t>1316: source value from HOSPITAL LOCATION - INSTITUTION &gt; DISTRICT (44-3 &gt; 4-.03)</t>
   </si>
   <si>
     <t>Dim.Institution.MedicalDistrict</t>
@@ -1213,7 +1213,7 @@
     <t>Address.state</t>
   </si>
   <si>
-    <t>1315: source value from HOSPITAL LOCATION - INSTITUTION &gt; STATE &gt; STATE - ABBREVIATION (#44-3 &gt; 4-.02 &gt; 5-1)</t>
+    <t>1315: source value from HOSPITAL LOCATION - INSTITUTION &gt; STATE &gt; STATE - ABBREVIATION (44-3 &gt; 4-.02 &gt; 5-1)</t>
   </si>
   <si>
     <t>AD.part[parttype = STA]</t>
@@ -1238,7 +1238,7 @@
     <t>Address.postalCode</t>
   </si>
   <si>
-    <t>1320: source value from HOSPITAL LOCATION - INSTITUTION &gt; ZIP (#44-3 &gt; 4-1.04)</t>
+    <t>1320: source value from HOSPITAL LOCATION - INSTITUTION &gt; ZIP (44-3 &gt; 4-1.04)</t>
   </si>
   <si>
     <t>Dim.Institution.Zip</t>
@@ -1262,7 +1262,7 @@
     <t>Address.country</t>
   </si>
   <si>
-    <t>1405: source value from HOSPITAL LOCATION - INSTITUTION &gt; COUNTRY &gt; COUNTRY - CODE (#44-3 &gt; 4-801 &gt; 779.004-0.1)</t>
+    <t>1405: source value from HOSPITAL LOCATION - INSTITUTION &gt; COUNTRY &gt; COUNTRY - CODE (44-3 &gt; 4-801 &gt; 779.004-0.1)</t>
   </si>
   <si>
     <t>AD.part[parttype = CNT]</t>
@@ -1325,7 +1325,7 @@
     <t>Location.physicalType.text</t>
   </si>
   <si>
-    <t>1284: source value from HOSPITAL LOCATION - PHYSICAL LOCATION (#44-10)</t>
+    <t>1284: source value from HOSPITAL LOCATION - PHYSICAL LOCATION (44-10)</t>
   </si>
   <si>
     <t>Dim.Location.PhysicalLocation</t>
@@ -1989,7 +1989,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="128.8515625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="127.3125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -928,11 +928,10 @@
     <t>ContactPoint.value</t>
   </si>
   <si>
-    <t>1280: transform using concat (44-99," ext. ",44-99.1) on HOSPITAL LOCATION - TELEPHONE &gt; TELEPHONE EXTENSION (44-99 &gt; 44-99.1)</t>
-  </si>
-  <si>
-    <t>Dim.Location.PhoneNumber
-Dim.Location.PhoneNumberExtension</t>
+    <t>1280: transform using concat (44-99," ext. ",44-99.1) on HOSPITAL LOCATION - TELEPHONE (44-99)</t>
+  </si>
+  <si>
+    <t>Dim.Location.PhoneNumber</t>
   </si>
   <si>
     <t>./url</t>
@@ -1123,7 +1122,7 @@
     <t>Address.line</t>
   </si>
   <si>
-    <t>1318: source value from HOSPITAL LOCATION - INSTITUTION &gt; STREET ADDR. 2 (44-3 &gt; 4-1.02)</t>
+    <t>1318: source value from HOSPITAL LOCATION - INSTITUTION &gt; INSTITUTION - STREET ADDR. 2 (44-3 &gt; 4-1.02)</t>
   </si>
   <si>
     <t>Dim.Institution.StreetAddress2</t>
@@ -1151,7 +1150,7 @@
     <t>Address.city</t>
   </si>
   <si>
-    <t>1319: source value from HOSPITAL LOCATION - INSTITUTION &gt; CITY (44-3 &gt; 4-1.03)</t>
+    <t>1319: source value from HOSPITAL LOCATION - INSTITUTION &gt; INSTITUTION - CITY (44-3 &gt; 4-1.03)</t>
   </si>
   <si>
     <t>Dim.Institution.City</t>
@@ -1182,7 +1181,7 @@
     <t>Address.district</t>
   </si>
   <si>
-    <t>1316: source value from HOSPITAL LOCATION - INSTITUTION &gt; DISTRICT (44-3 &gt; 4-.03)</t>
+    <t>1316: source value from HOSPITAL LOCATION - INSTITUTION &gt; INSTITUTION - DISTRICT (44-3 &gt; 4-.03)</t>
   </si>
   <si>
     <t>Dim.Institution.MedicalDistrict</t>
@@ -1213,7 +1212,7 @@
     <t>Address.state</t>
   </si>
   <si>
-    <t>1315: source value from HOSPITAL LOCATION - INSTITUTION &gt; STATE &gt; STATE - ABBREVIATION (44-3 &gt; 4-.02 &gt; 5-1)</t>
+    <t>1315: source value from HOSPITAL LOCATION - INSTITUTION &gt; INSTITUTION - STATE &gt; STATE - ABBREVIATION (44-3 &gt; 4-.02 &gt; 5-1)</t>
   </si>
   <si>
     <t>AD.part[parttype = STA]</t>
@@ -1238,7 +1237,7 @@
     <t>Address.postalCode</t>
   </si>
   <si>
-    <t>1320: source value from HOSPITAL LOCATION - INSTITUTION &gt; ZIP (44-3 &gt; 4-1.04)</t>
+    <t>1320: source value from HOSPITAL LOCATION - INSTITUTION &gt; INSTITUTION - ZIP (44-3 &gt; 4-1.04)</t>
   </si>
   <si>
     <t>Dim.Institution.Zip</t>
@@ -1262,7 +1261,7 @@
     <t>Address.country</t>
   </si>
   <si>
-    <t>1405: source value from HOSPITAL LOCATION - INSTITUTION &gt; COUNTRY &gt; COUNTRY - CODE (44-3 &gt; 4-801 &gt; 779.004-0.1)</t>
+    <t>1405: source value from HOSPITAL LOCATION - INSTITUTION &gt; INSTITUTION - COUNTRY &gt; COUNTRY - CODE (44-3 &gt; 4-801 &gt; 779.004-0.1)</t>
   </si>
   <si>
     <t>AD.part[parttype = CNT]</t>
@@ -1989,7 +1988,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="127.3125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="128.671875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2945" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2945" uniqueCount="525">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -785,7 +785,13 @@
     <t>When using a Location resource for scheduling or orders, we need to be able to refer to a class of Locations instead of a specific Location.</t>
   </si>
   <si>
+    <t>instance</t>
+  </si>
+  <si>
     <t>http://hl7.org/fhir/ValueSet/location-mode|4.0.1</t>
+  </si>
+  <si>
+    <t>1806: fixed value = #instance</t>
   </si>
   <si>
     <t>.playingEntity[classCode=PLC].determinerCode</t>
@@ -1261,7 +1267,7 @@
     <t>Address.country</t>
   </si>
   <si>
-    <t>1405: source value from HOSPITAL LOCATION - INSTITUTION &gt; INSTITUTION - COUNTRY &gt; COUNTRY - CODE (44-3 &gt; 4-801 &gt; 779.004-0.1)</t>
+    <t>1405: source value from HOSPITAL LOCATION - INSTITUTION &gt; INSTITUTION - COUNTRY &gt; COUNTRY - CODE (44-3 &gt; 4-801 &gt; 779.004-.01)</t>
   </si>
   <si>
     <t>AD.part[parttype = CNT]</t>
@@ -4755,7 +4761,7 @@
         <v>84</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>75</v>
@@ -4786,7 +4792,7 @@
         <v>75</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>75</v>
+        <v>248</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>75</v>
@@ -4807,7 +4813,7 @@
         <v>245</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>75</v>
@@ -4840,24 +4846,24 @@
         <v>96</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>75</v>
+        <v>250</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4883,10 +4889,10 @@
         <v>171</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4916,28 +4922,28 @@
         <v>176</v>
       </c>
       <c r="Y26" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -4958,18 +4964,18 @@
         <v>75</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5078,10 +5084,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5192,10 +5198,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5221,16 +5227,16 @@
         <v>217</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>75</v>
@@ -5279,7 +5285,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -5300,7 +5306,7 @@
         <v>75</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>75</v>
@@ -5308,10 +5314,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5337,16 +5343,16 @@
         <v>149</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>75</v>
@@ -5393,7 +5399,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -5408,13 +5414,13 @@
         <v>96</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>75</v>
@@ -5422,10 +5428,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5448,13 +5454,13 @@
         <v>75</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5505,7 +5511,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -5526,7 +5532,7 @@
         <v>75</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>75</v>
@@ -5534,10 +5540,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5646,10 +5652,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5760,10 +5766,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5789,10 +5795,10 @@
         <v>104</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5822,10 +5828,10 @@
         <v>165</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>75</v>
@@ -5843,7 +5849,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -5852,7 +5858,7 @@
         <v>84</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>96</v>
@@ -5864,7 +5870,7 @@
         <v>75</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>75</v>
@@ -5872,10 +5878,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5901,16 +5907,16 @@
         <v>149</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>75</v>
@@ -5959,7 +5965,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -5974,13 +5980,13 @@
         <v>96</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>75</v>
@@ -5988,10 +5994,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6017,16 +6023,16 @@
         <v>104</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>75</v>
@@ -6054,10 +6060,10 @@
         <v>165</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>75</v>
@@ -6075,7 +6081,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -6096,7 +6102,7 @@
         <v>75</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>75</v>
@@ -6104,10 +6110,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6130,16 +6136,16 @@
         <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6189,7 +6195,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -6218,10 +6224,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6247,10 +6253,10 @@
         <v>197</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6301,7 +6307,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -6322,7 +6328,7 @@
         <v>75</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>75</v>
@@ -6330,10 +6336,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6356,19 +6362,19 @@
         <v>75</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>75</v>
@@ -6417,7 +6423,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -6438,7 +6444,7 @@
         <v>75</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>75</v>
@@ -6446,10 +6452,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6558,10 +6564,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6672,10 +6678,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6701,16 +6707,16 @@
         <v>104</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>75</v>
@@ -6723,7 +6729,7 @@
         <v>75</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>75</v>
@@ -6738,10 +6744,10 @@
         <v>165</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>75</v>
@@ -6759,7 +6765,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -6780,7 +6786,7 @@
         <v>75</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>75</v>
@@ -6788,10 +6794,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6817,13 +6823,13 @@
         <v>104</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6834,10 +6840,10 @@
         <v>75</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="U43" t="s" s="2">
         <v>75</v>
@@ -6852,10 +6858,10 @@
         <v>165</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>75</v>
@@ -6873,7 +6879,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -6888,13 +6894,13 @@
         <v>96</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>75</v>
@@ -6902,10 +6908,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6931,16 +6937,16 @@
         <v>149</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>75</v>
@@ -6953,7 +6959,7 @@
         <v>75</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>75</v>
@@ -6989,7 +6995,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -7010,7 +7016,7 @@
         <v>75</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>75</v>
@@ -7018,10 +7024,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7047,10 +7053,10 @@
         <v>149</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7065,7 +7071,7 @@
         <v>75</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>75</v>
@@ -7101,7 +7107,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -7116,13 +7122,13 @@
         <v>96</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>75</v>
@@ -7130,14 +7136,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7159,10 +7165,10 @@
         <v>149</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7177,7 +7183,7 @@
         <v>75</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>75</v>
@@ -7213,7 +7219,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -7228,13 +7234,13 @@
         <v>96</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>75</v>
@@ -7242,14 +7248,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7271,13 +7277,13 @@
         <v>149</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7291,7 +7297,7 @@
         <v>75</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>75</v>
@@ -7327,7 +7333,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -7342,13 +7348,13 @@
         <v>96</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>75</v>
@@ -7356,14 +7362,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7385,10 +7391,10 @@
         <v>149</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7418,10 +7424,10 @@
         <v>176</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>75</v>
@@ -7439,7 +7445,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -7454,13 +7460,13 @@
         <v>96</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>75</v>
@@ -7468,14 +7474,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7497,10 +7503,10 @@
         <v>149</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7515,7 +7521,7 @@
         <v>75</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="U49" t="s" s="2">
         <v>75</v>
@@ -7551,7 +7557,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -7566,13 +7572,13 @@
         <v>96</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>75</v>
@@ -7580,10 +7586,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7609,13 +7615,13 @@
         <v>149</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7665,7 +7671,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -7680,13 +7686,13 @@
         <v>96</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>75</v>
@@ -7694,10 +7700,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7723,14 +7729,14 @@
         <v>197</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>75</v>
@@ -7743,7 +7749,7 @@
         <v>75</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>75</v>
@@ -7779,7 +7785,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -7800,7 +7806,7 @@
         <v>75</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>75</v>
@@ -7808,10 +7814,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7837,14 +7843,14 @@
         <v>171</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>75</v>
@@ -7869,13 +7875,13 @@
         <v>75</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>75</v>
@@ -7893,7 +7899,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -7914,18 +7920,18 @@
         <v>75</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8034,10 +8040,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8148,10 +8154,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8177,16 +8183,16 @@
         <v>217</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>75</v>
@@ -8235,7 +8241,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -8256,7 +8262,7 @@
         <v>75</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>75</v>
@@ -8264,10 +8270,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8293,16 +8299,16 @@
         <v>149</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>75</v>
@@ -8351,7 +8357,7 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -8366,13 +8372,13 @@
         <v>96</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>75</v>
@@ -8380,10 +8386,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8406,17 +8412,17 @@
         <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>75</v>
@@ -8465,7 +8471,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -8486,7 +8492,7 @@
         <v>75</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>75</v>
@@ -8494,10 +8500,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8606,10 +8612,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8720,14 +8726,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8749,10 +8755,10 @@
         <v>130</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>133</v>
@@ -8807,7 +8813,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -8836,10 +8842,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8862,13 +8868,13 @@
         <v>75</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8919,7 +8925,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>84</v>
@@ -8940,7 +8946,7 @@
         <v>75</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>75</v>
@@ -8948,10 +8954,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8974,13 +8980,13 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9031,7 +9037,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>84</v>
@@ -9052,7 +9058,7 @@
         <v>75</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>75</v>
@@ -9060,10 +9066,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9086,13 +9092,13 @@
         <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9143,7 +9149,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -9164,7 +9170,7 @@
         <v>75</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>75</v>
@@ -9172,10 +9178,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9198,19 +9204,19 @@
         <v>85</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>75</v>
@@ -9259,7 +9265,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -9280,7 +9286,7 @@
         <v>75</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>75</v>
@@ -9288,10 +9294,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9400,10 +9406,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9514,10 +9520,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9543,13 +9549,13 @@
         <v>149</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9599,7 +9605,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -9608,7 +9614,7 @@
         <v>84</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>96</v>
@@ -9628,10 +9634,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9657,13 +9663,13 @@
         <v>98</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9692,10 +9698,10 @@
         <v>176</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>75</v>
@@ -9713,7 +9719,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -9742,10 +9748,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9771,13 +9777,13 @@
         <v>142</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9827,7 +9833,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -9848,7 +9854,7 @@
         <v>75</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>75</v>
@@ -9856,10 +9862,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9885,13 +9891,13 @@
         <v>149</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9902,7 +9908,7 @@
         <v>75</v>
       </c>
       <c r="S70" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="T70" t="s" s="2">
         <v>75</v>
@@ -9941,7 +9947,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -9956,7 +9962,7 @@
         <v>96</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>75</v>
@@ -9970,10 +9976,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9996,17 +10002,17 @@
         <v>75</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>75</v>
@@ -10055,7 +10061,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -10076,7 +10082,7 @@
         <v>75</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>75</v>
@@ -10084,10 +10090,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10110,16 +10116,16 @@
         <v>75</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10169,7 +10175,7 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
@@ -10190,7 +10196,7 @@
         <v>75</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>75</v>
@@ -10198,10 +10204,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10310,10 +10316,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10424,14 +10430,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10453,10 +10459,10 @@
         <v>130</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>133</v>
@@ -10511,7 +10517,7 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
@@ -10540,10 +10546,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10569,10 +10575,10 @@
         <v>104</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10602,10 +10608,10 @@
         <v>165</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>75</v>
@@ -10623,7 +10629,7 @@
         <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -10644,7 +10650,7 @@
         <v>75</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>75</v>
@@ -10652,10 +10658,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10678,13 +10684,13 @@
         <v>75</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10735,7 +10741,7 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
@@ -10756,7 +10762,7 @@
         <v>75</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>75</v>
@@ -10764,10 +10770,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10790,13 +10796,13 @@
         <v>75</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10847,7 +10853,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
@@ -10868,7 +10874,7 @@
         <v>75</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>75</v>
@@ -10876,10 +10882,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10902,13 +10908,13 @@
         <v>75</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -10959,7 +10965,7 @@
         <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
@@ -10980,7 +10986,7 @@
         <v>75</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>75</v>
@@ -10988,10 +10994,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11017,10 +11023,10 @@
         <v>149</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11071,7 +11077,7 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
@@ -11100,10 +11106,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11126,17 +11132,17 @@
         <v>75</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>75</v>
@@ -11185,7 +11191,7 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1267,7 +1267,7 @@
     <t>Address.country</t>
   </si>
   <si>
-    <t>1405: source value from HOSPITAL LOCATION - INSTITUTION &gt; INSTITUTION - COUNTRY &gt; COUNTRY - CODE (44-3 &gt; 4-801 &gt; 779.004-.01)</t>
+    <t>1405: source value from HOSPITAL LOCATION - INSTITUTION &gt; INSTITUTION - COUNTRY &gt; COUNTRY CODE - CODE (44-3 &gt; 4-801 &gt; 779.004-.01)</t>
   </si>
   <si>
     <t>AD.part[parttype = CNT]</t>
@@ -1994,7 +1994,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="128.671875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="134.546875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2945" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2945" uniqueCount="526">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -721,7 +721,7 @@
     <t>756: source value from HOSPITAL LOCATION - NAME (44-.01)</t>
   </si>
   <si>
-    <t>Dim.Location.LocationName</t>
+    <t>Dim.Location.LocationName,Dim.Location.LocationName</t>
   </si>
   <si>
     <t>.name</t>
@@ -746,7 +746,7 @@
     <t>1277: source value from HOSPITAL LOCATION - SYNONYM (44-13)</t>
   </si>
   <si>
-    <t>Dim.Location.LocationAbbreviation</t>
+    <t>Dim.Location.LocationAbbreviation,Dim.Location.LocationAbbreviation</t>
   </si>
   <si>
     <t>Location.description</t>
@@ -764,7 +764,7 @@
     <t>1279: source value from HOSPITAL LOCATION - PATIENT FRIENDLY NAME (44-60)</t>
   </si>
   <si>
-    <t>Dim.Location.PatientFriendlyLocationName</t>
+    <t>Dim.Location.PatientFriendlyLocationName,Dim.Location.PatientFriendlyLocationName</t>
   </si>
   <si>
     <t>.playingEntity[classCode=PLC determinerCode=INSTANCE].desc</t>
@@ -863,7 +863,7 @@
     <t>1412: terminologyMaps using VF_LocationStatus on HOSPITAL LOCATION - SERVICE (44-9)</t>
   </si>
   <si>
-    <t>Dim.Location.MedicalService</t>
+    <t>Dim.Location.MedicalService,Dim.Location.MedicalService</t>
   </si>
   <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
@@ -937,7 +937,7 @@
     <t>1280: transform using concat (44-99," ext. ",44-99.1) on HOSPITAL LOCATION - TELEPHONE (44-99)</t>
   </si>
   <si>
-    <t>Dim.Location.PhoneNumber</t>
+    <t>Dim.Location.PhoneNumber,Dim.Location.PhoneNumber</t>
   </si>
   <si>
     <t>./url</t>
@@ -1089,6 +1089,9 @@
     <t>1322: fixed value = #physical when HOSPITAL LOCATION - INSTITUTION (44-3)</t>
   </si>
   <si>
+    <t>Dim.Location.InstitutionIEN</t>
+  </si>
+  <si>
     <t>Location.address.text</t>
   </si>
   <si>
@@ -1131,7 +1134,8 @@
     <t>1318: source value from HOSPITAL LOCATION - INSTITUTION &gt; INSTITUTION - STREET ADDR. 2 (44-3 &gt; 4-1.02)</t>
   </si>
   <si>
-    <t>Dim.Institution.StreetAddress2</t>
+    <t>Dim.Location.InstitutionIEN
+Dim.Institution.StreetAddress2,Dim.Institution.StreetAddress2,Dim.InstitutionTimeZone.StreetAddress2,NDim.MVIInstitution.StreetAddress2</t>
   </si>
   <si>
     <t>AD.part[parttype = AL]</t>
@@ -1159,7 +1163,8 @@
     <t>1319: source value from HOSPITAL LOCATION - INSTITUTION &gt; INSTITUTION - CITY (44-3 &gt; 4-1.03)</t>
   </si>
   <si>
-    <t>Dim.Institution.City</t>
+    <t>Dim.Location.InstitutionIEN
+Dim.Institution.City,Dim.Institution.City,Dim.InstitutionTimeZone.City,NDim.MVIInstitution.City</t>
   </si>
   <si>
     <t>AD.part[parttype = CTY]</t>
@@ -1190,7 +1195,8 @@
     <t>1316: source value from HOSPITAL LOCATION - INSTITUTION &gt; INSTITUTION - DISTRICT (44-3 &gt; 4-.03)</t>
   </si>
   <si>
-    <t>Dim.Institution.MedicalDistrict</t>
+    <t>Dim.Location.InstitutionIEN
+Dim.Institution.MedicalDistrict,Dim.Institution.MedicalDistrict,NDim.MVIInstitution.MedicalDistrict</t>
   </si>
   <si>
     <t>AD.part[parttype = CNT | CPA]</t>
@@ -1246,7 +1252,8 @@
     <t>1320: source value from HOSPITAL LOCATION - INSTITUTION &gt; INSTITUTION - ZIP (44-3 &gt; 4-1.04)</t>
   </si>
   <si>
-    <t>Dim.Institution.Zip</t>
+    <t>Dim.Location.InstitutionIEN
+Dim.Institution.Zip,Dim.Institution.Zip,Dim.InstitutionTimeZone.Zip,NDim.MVIInstitution.Zip</t>
   </si>
   <si>
     <t>AD.part[parttype = ZIP]</t>
@@ -1333,7 +1340,7 @@
     <t>1284: source value from HOSPITAL LOCATION - PHYSICAL LOCATION (44-10)</t>
   </si>
   <si>
-    <t>Dim.Location.PhysicalLocation</t>
+    <t>Dim.Location.PhysicalLocation,Dim.Location.PhysicalLocation</t>
   </si>
   <si>
     <t>Location.position</t>
@@ -1995,7 +2002,7 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="134.546875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="129.9609375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
   </cols>
@@ -6897,7 +6904,7 @@
         <v>347</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>75</v>
+        <v>348</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>308</v>
@@ -6908,10 +6915,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6937,16 +6944,16 @@
         <v>149</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>75</v>
@@ -6959,7 +6966,7 @@
         <v>75</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>75</v>
@@ -6995,7 +7002,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -7016,7 +7023,7 @@
         <v>75</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>75</v>
@@ -7024,10 +7031,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7053,10 +7060,10 @@
         <v>149</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7071,7 +7078,7 @@
         <v>75</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>75</v>
@@ -7107,7 +7114,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -7122,13 +7129,13 @@
         <v>96</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>75</v>
@@ -7136,14 +7143,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7165,10 +7172,10 @@
         <v>149</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7183,7 +7190,7 @@
         <v>75</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>75</v>
@@ -7219,7 +7226,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -7234,13 +7241,13 @@
         <v>96</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>75</v>
@@ -7248,14 +7255,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7277,13 +7284,13 @@
         <v>149</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7297,7 +7304,7 @@
         <v>75</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>75</v>
@@ -7333,7 +7340,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -7348,13 +7355,13 @@
         <v>96</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>75</v>
@@ -7362,14 +7369,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7391,10 +7398,10 @@
         <v>149</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7424,10 +7431,10 @@
         <v>176</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>75</v>
@@ -7445,7 +7452,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -7460,13 +7467,13 @@
         <v>96</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>75</v>
+        <v>348</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>75</v>
@@ -7474,14 +7481,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7503,10 +7510,10 @@
         <v>149</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7521,7 +7528,7 @@
         <v>75</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="U49" t="s" s="2">
         <v>75</v>
@@ -7557,7 +7564,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -7572,13 +7579,13 @@
         <v>96</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>75</v>
@@ -7586,10 +7593,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7615,13 +7622,13 @@
         <v>149</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7671,7 +7678,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -7686,13 +7693,13 @@
         <v>96</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>75</v>
+        <v>348</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>75</v>
@@ -7700,10 +7707,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7729,14 +7736,14 @@
         <v>197</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>75</v>
@@ -7749,7 +7756,7 @@
         <v>75</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>75</v>
@@ -7785,7 +7792,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -7814,10 +7821,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7843,14 +7850,14 @@
         <v>171</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>75</v>
@@ -7875,13 +7882,13 @@
         <v>75</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>75</v>
@@ -7899,7 +7906,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -7920,7 +7927,7 @@
         <v>75</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>252</v>
@@ -7928,10 +7935,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8040,10 +8047,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8154,10 +8161,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8270,10 +8277,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8372,10 +8379,10 @@
         <v>96</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>275</v>
@@ -8386,10 +8393,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8412,17 +8419,17 @@
         <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>75</v>
@@ -8471,7 +8478,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -8492,7 +8499,7 @@
         <v>75</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>75</v>
@@ -8500,10 +8507,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8612,10 +8619,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8726,14 +8733,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8755,10 +8762,10 @@
         <v>130</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>133</v>
@@ -8813,7 +8820,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -8842,10 +8849,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8868,13 +8875,13 @@
         <v>75</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8925,7 +8932,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>84</v>
@@ -8946,7 +8953,7 @@
         <v>75</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>75</v>
@@ -8954,10 +8961,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8980,13 +8987,13 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9037,7 +9044,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>84</v>
@@ -9058,7 +9065,7 @@
         <v>75</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>75</v>
@@ -9066,10 +9073,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9092,13 +9099,13 @@
         <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9149,7 +9156,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -9170,7 +9177,7 @@
         <v>75</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>75</v>
@@ -9178,10 +9185,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9204,19 +9211,19 @@
         <v>85</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>75</v>
@@ -9265,7 +9272,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -9286,7 +9293,7 @@
         <v>75</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>75</v>
@@ -9294,10 +9301,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9406,10 +9413,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9520,10 +9527,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9549,13 +9556,13 @@
         <v>149</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9605,7 +9612,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -9614,7 +9621,7 @@
         <v>84</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>96</v>
@@ -9634,10 +9641,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9663,13 +9670,13 @@
         <v>98</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9698,10 +9705,10 @@
         <v>176</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>75</v>
@@ -9719,7 +9726,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -9748,10 +9755,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9777,13 +9784,13 @@
         <v>142</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9833,7 +9840,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -9854,7 +9861,7 @@
         <v>75</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>75</v>
@@ -9862,10 +9869,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9891,13 +9898,13 @@
         <v>149</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9908,7 +9915,7 @@
         <v>75</v>
       </c>
       <c r="S70" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="T70" t="s" s="2">
         <v>75</v>
@@ -9947,7 +9954,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -9962,7 +9969,7 @@
         <v>96</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>75</v>
@@ -9976,10 +9983,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10002,17 +10009,17 @@
         <v>75</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>75</v>
@@ -10061,7 +10068,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -10082,7 +10089,7 @@
         <v>75</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>75</v>
@@ -10090,10 +10097,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10116,16 +10123,16 @@
         <v>75</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10175,7 +10182,7 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
@@ -10196,7 +10203,7 @@
         <v>75</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>75</v>
@@ -10204,10 +10211,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10316,10 +10323,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10430,14 +10437,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10459,10 +10466,10 @@
         <v>130</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>133</v>
@@ -10517,7 +10524,7 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
@@ -10546,10 +10553,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10575,10 +10582,10 @@
         <v>104</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10608,10 +10615,10 @@
         <v>165</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>75</v>
@@ -10629,7 +10636,7 @@
         <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -10650,7 +10657,7 @@
         <v>75</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>75</v>
@@ -10658,10 +10665,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10684,13 +10691,13 @@
         <v>75</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10741,7 +10748,7 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
@@ -10762,7 +10769,7 @@
         <v>75</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>75</v>
@@ -10770,10 +10777,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10796,13 +10803,13 @@
         <v>75</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10853,7 +10860,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
@@ -10874,7 +10881,7 @@
         <v>75</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>75</v>
@@ -10882,10 +10889,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10908,13 +10915,13 @@
         <v>75</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -10965,7 +10972,7 @@
         <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
@@ -10986,7 +10993,7 @@
         <v>75</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>75</v>
@@ -10994,10 +11001,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11023,10 +11030,10 @@
         <v>149</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11077,7 +11084,7 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
@@ -11106,10 +11113,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11132,17 +11139,17 @@
         <v>75</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>75</v>
@@ -11191,7 +11198,7 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2945" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2945" uniqueCount="532">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -592,10 +592,16 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
+    <t>http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/44</t>
+  </si>
+  <si>
     <t>http://www.acme.com/identifiers/patient</t>
   </si>
   <si>
     <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>755-1: fixed value = http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/44</t>
   </si>
   <si>
     <t>II.root or Role.id.root</t>
@@ -900,6 +906,9 @@
     <t>Telecommunications form for contact point - what communications system is required to make use of the contact.</t>
   </si>
   <si>
+    <t>phone</t>
+  </si>
+  <si>
     <t>Telecommunications form for contact point.</t>
   </si>
   <si>
@@ -913,6 +922,9 @@
 </t>
   </si>
   <si>
+    <t>1280-1: fixed value = #phone</t>
+  </si>
+  <si>
     <t>./scheme</t>
   </si>
   <si>
@@ -958,6 +970,9 @@
     <t>Need to track the way a person uses this contact, so a user can choose which is appropriate for their purpose.</t>
   </si>
   <si>
+    <t>work</t>
+  </si>
+  <si>
     <t>Use of contact point.</t>
   </si>
   <si>
@@ -965,6 +980,9 @@
   </si>
   <si>
     <t>ContactPoint.use</t>
+  </si>
+  <si>
+    <t>1280-2: fixed value = #work</t>
   </si>
   <si>
     <t>unique(./use)</t>
@@ -3746,7 +3764,7 @@
         <v>84</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>75</v>
@@ -3777,10 +3795,10 @@
         <v>75</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>75</v>
+        <v>185</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>75</v>
@@ -3816,7 +3834,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -3831,13 +3849,13 @@
         <v>96</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>75</v>
+        <v>188</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>75</v>
@@ -3845,10 +3863,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3874,13 +3892,13 @@
         <v>149</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3894,7 +3912,7 @@
         <v>75</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>75</v>
@@ -3930,7 +3948,7 @@
         <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -3945,13 +3963,13 @@
         <v>96</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>75</v>
@@ -3959,10 +3977,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3985,13 +4003,13 @@
         <v>85</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4042,7 +4060,7 @@
         <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -4063,7 +4081,7 @@
         <v>75</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>75</v>
@@ -4071,10 +4089,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4097,16 +4115,16 @@
         <v>85</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4156,7 +4174,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -4177,7 +4195,7 @@
         <v>75</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>75</v>
@@ -4185,10 +4203,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4214,10 +4232,10 @@
         <v>104</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4248,7 +4266,7 @@
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>75</v>
@@ -4266,7 +4284,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -4281,24 +4299,24 @@
         <v>96</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4321,13 +4339,13 @@
         <v>85</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4357,10 +4375,10 @@
         <v>108</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>75</v>
@@ -4378,7 +4396,7 @@
         <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -4402,15 +4420,15 @@
         <v>153</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4436,13 +4454,13 @@
         <v>149</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4492,7 +4510,7 @@
         <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -4507,13 +4525,13 @@
         <v>96</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>75</v>
@@ -4521,10 +4539,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4550,16 +4568,16 @@
         <v>149</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>75</v>
@@ -4608,7 +4626,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -4623,13 +4641,13 @@
         <v>96</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>75</v>
@@ -4637,10 +4655,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4666,14 +4684,14 @@
         <v>149</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>75</v>
@@ -4722,7 +4740,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -4737,13 +4755,13 @@
         <v>96</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>75</v>
@@ -4751,10 +4769,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4780,16 +4798,16 @@
         <v>104</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>75</v>
@@ -4799,7 +4817,7 @@
         <v>75</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>75</v>
@@ -4817,28 +4835,28 @@
         <v>165</v>
       </c>
       <c r="Y25" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -4853,24 +4871,24 @@
         <v>96</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4896,10 +4914,10 @@
         <v>171</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4929,28 +4947,28 @@
         <v>176</v>
       </c>
       <c r="Y26" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -4971,18 +4989,18 @@
         <v>75</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5091,10 +5109,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5205,10 +5223,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5231,19 +5249,19 @@
         <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>75</v>
@@ -5292,7 +5310,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -5313,7 +5331,7 @@
         <v>75</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>75</v>
@@ -5321,10 +5339,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5350,16 +5368,16 @@
         <v>149</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>75</v>
@@ -5388,7 +5406,7 @@
       </c>
       <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>75</v>
@@ -5406,7 +5424,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -5421,13 +5439,13 @@
         <v>96</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>75</v>
@@ -5435,10 +5453,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5461,13 +5479,13 @@
         <v>75</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5518,7 +5536,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -5539,7 +5557,7 @@
         <v>75</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>75</v>
@@ -5547,10 +5565,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5659,10 +5677,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5773,10 +5791,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5790,7 +5808,7 @@
         <v>84</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>75</v>
@@ -5802,10 +5820,10 @@
         <v>104</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5817,7 +5835,7 @@
         <v>75</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>75</v>
+        <v>288</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>75</v>
@@ -5835,10 +5853,10 @@
         <v>165</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>75</v>
@@ -5856,7 +5874,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -5865,19 +5883,19 @@
         <v>84</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>75</v>
+        <v>293</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>75</v>
@@ -5885,10 +5903,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5914,16 +5932,16 @@
         <v>149</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>75</v>
@@ -5972,7 +5990,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -5987,13 +6005,13 @@
         <v>96</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>75</v>
@@ -6001,10 +6019,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6018,7 +6036,7 @@
         <v>84</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>85</v>
@@ -6030,16 +6048,16 @@
         <v>104</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>75</v>
@@ -6049,7 +6067,7 @@
         <v>75</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>75</v>
+        <v>309</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>75</v>
@@ -6067,10 +6085,10 @@
         <v>165</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>75</v>
@@ -6088,7 +6106,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -6103,13 +6121,13 @@
         <v>96</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>75</v>
+        <v>313</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>75</v>
@@ -6117,10 +6135,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6143,16 +6161,16 @@
         <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6202,7 +6220,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -6231,10 +6249,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6257,13 +6275,13 @@
         <v>85</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6314,7 +6332,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -6335,7 +6353,7 @@
         <v>75</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>75</v>
@@ -6343,10 +6361,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6369,19 +6387,19 @@
         <v>75</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>75</v>
@@ -6430,7 +6448,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -6451,7 +6469,7 @@
         <v>75</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>75</v>
@@ -6459,10 +6477,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6571,10 +6589,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6685,10 +6703,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6714,16 +6732,16 @@
         <v>104</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>75</v>
@@ -6736,7 +6754,7 @@
         <v>75</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>75</v>
@@ -6751,10 +6769,10 @@
         <v>165</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>75</v>
@@ -6772,7 +6790,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -6793,7 +6811,7 @@
         <v>75</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>75</v>
@@ -6801,10 +6819,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6830,13 +6848,13 @@
         <v>104</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6847,10 +6865,10 @@
         <v>75</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="U43" t="s" s="2">
         <v>75</v>
@@ -6865,10 +6883,10 @@
         <v>165</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>75</v>
@@ -6886,7 +6904,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -6901,13 +6919,13 @@
         <v>96</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>75</v>
@@ -6915,10 +6933,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6944,16 +6962,16 @@
         <v>149</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>75</v>
@@ -6966,7 +6984,7 @@
         <v>75</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>75</v>
@@ -7002,7 +7020,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -7023,7 +7041,7 @@
         <v>75</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>75</v>
@@ -7031,10 +7049,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7060,10 +7078,10 @@
         <v>149</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7078,7 +7096,7 @@
         <v>75</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>75</v>
@@ -7114,7 +7132,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -7129,13 +7147,13 @@
         <v>96</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>75</v>
@@ -7143,14 +7161,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7172,10 +7190,10 @@
         <v>149</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7190,7 +7208,7 @@
         <v>75</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>75</v>
@@ -7226,7 +7244,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -7241,13 +7259,13 @@
         <v>96</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>75</v>
@@ -7255,14 +7273,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7284,13 +7302,13 @@
         <v>149</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7304,7 +7322,7 @@
         <v>75</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>75</v>
@@ -7340,7 +7358,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -7355,13 +7373,13 @@
         <v>96</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>75</v>
@@ -7369,14 +7387,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7398,10 +7416,10 @@
         <v>149</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7431,10 +7449,10 @@
         <v>176</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>75</v>
@@ -7452,7 +7470,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -7467,13 +7485,13 @@
         <v>96</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>75</v>
@@ -7481,14 +7499,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7510,10 +7528,10 @@
         <v>149</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7528,7 +7546,7 @@
         <v>75</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="U49" t="s" s="2">
         <v>75</v>
@@ -7564,7 +7582,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -7579,13 +7597,13 @@
         <v>96</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>75</v>
@@ -7593,10 +7611,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7622,13 +7640,13 @@
         <v>149</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7678,7 +7696,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -7693,13 +7711,13 @@
         <v>96</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>75</v>
@@ -7707,10 +7725,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7733,17 +7751,17 @@
         <v>85</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>75</v>
@@ -7756,7 +7774,7 @@
         <v>75</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>75</v>
@@ -7792,7 +7810,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -7813,7 +7831,7 @@
         <v>75</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>75</v>
@@ -7821,10 +7839,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7850,14 +7868,14 @@
         <v>171</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>75</v>
@@ -7882,31 +7900,31 @@
         <v>75</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="Z52" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -7927,18 +7945,18 @@
         <v>75</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8047,10 +8065,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8161,10 +8179,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8187,19 +8205,19 @@
         <v>85</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>75</v>
@@ -8248,7 +8266,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -8269,7 +8287,7 @@
         <v>75</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>75</v>
@@ -8277,10 +8295,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8306,16 +8324,16 @@
         <v>149</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>75</v>
@@ -8364,7 +8382,7 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -8379,13 +8397,13 @@
         <v>96</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>75</v>
@@ -8393,10 +8411,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8419,17 +8437,17 @@
         <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>75</v>
@@ -8478,7 +8496,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -8499,7 +8517,7 @@
         <v>75</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>75</v>
@@ -8507,10 +8525,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8619,10 +8637,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8733,14 +8751,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8762,10 +8780,10 @@
         <v>130</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>133</v>
@@ -8820,7 +8838,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -8849,10 +8867,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8875,13 +8893,13 @@
         <v>75</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8932,7 +8950,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>84</v>
@@ -8953,7 +8971,7 @@
         <v>75</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>75</v>
@@ -8961,10 +8979,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8987,13 +9005,13 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9044,7 +9062,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>84</v>
@@ -9065,7 +9083,7 @@
         <v>75</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>75</v>
@@ -9073,10 +9091,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9099,13 +9117,13 @@
         <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9156,7 +9174,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -9177,7 +9195,7 @@
         <v>75</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>75</v>
@@ -9185,10 +9203,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9211,19 +9229,19 @@
         <v>85</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>75</v>
@@ -9272,7 +9290,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -9293,7 +9311,7 @@
         <v>75</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>75</v>
@@ -9301,10 +9319,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9413,10 +9431,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9527,10 +9545,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9556,13 +9574,13 @@
         <v>149</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9612,7 +9630,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -9621,7 +9639,7 @@
         <v>84</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>96</v>
@@ -9641,10 +9659,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9670,13 +9688,13 @@
         <v>98</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9705,10 +9723,10 @@
         <v>176</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>75</v>
@@ -9726,7 +9744,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -9755,10 +9773,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9784,13 +9802,13 @@
         <v>142</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9840,7 +9858,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -9861,7 +9879,7 @@
         <v>75</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>75</v>
@@ -9869,10 +9887,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9898,13 +9916,13 @@
         <v>149</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9915,7 +9933,7 @@
         <v>75</v>
       </c>
       <c r="S70" t="s" s="2">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="T70" t="s" s="2">
         <v>75</v>
@@ -9954,7 +9972,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -9969,7 +9987,7 @@
         <v>96</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>75</v>
@@ -9983,10 +10001,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10009,17 +10027,17 @@
         <v>75</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>75</v>
@@ -10068,7 +10086,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -10089,7 +10107,7 @@
         <v>75</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>75</v>
@@ -10097,10 +10115,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10123,16 +10141,16 @@
         <v>75</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10182,7 +10200,7 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
@@ -10203,7 +10221,7 @@
         <v>75</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>75</v>
@@ -10211,10 +10229,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10323,10 +10341,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10437,14 +10455,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10466,10 +10484,10 @@
         <v>130</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>133</v>
@@ -10524,7 +10542,7 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
@@ -10553,10 +10571,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10582,10 +10600,10 @@
         <v>104</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10615,10 +10633,10 @@
         <v>165</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>75</v>
@@ -10636,7 +10654,7 @@
         <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -10657,7 +10675,7 @@
         <v>75</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>75</v>
@@ -10665,10 +10683,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10691,13 +10709,13 @@
         <v>75</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10748,7 +10766,7 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
@@ -10769,7 +10787,7 @@
         <v>75</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>75</v>
@@ -10777,10 +10795,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10803,13 +10821,13 @@
         <v>75</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10860,7 +10878,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
@@ -10881,7 +10899,7 @@
         <v>75</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>75</v>
@@ -10889,10 +10907,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10915,13 +10933,13 @@
         <v>75</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -10972,7 +10990,7 @@
         <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
@@ -10993,7 +11011,7 @@
         <v>75</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>75</v>
@@ -11001,10 +11019,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11030,10 +11048,10 @@
         <v>149</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11084,7 +11102,7 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
@@ -11113,10 +11131,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11139,17 +11157,17 @@
         <v>75</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>75</v>
@@ -11198,7 +11216,7 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -592,7 +592,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/44</t>
+    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/44</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -601,7 +601,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>755-1: fixed value = http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/44</t>
+    <t>755-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/44</t>
   </si>
   <si>
     <t>II.root or Role.id.root</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -592,7 +592,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/44</t>
+    <t>http://va.gov/identifiers/$Sta3n/44</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -601,7 +601,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>755-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/44</t>
+    <t>755-1: fixed value = http://va.gov/identifiers/$Sta3n/44</t>
   </si>
   <si>
     <t>II.root or Role.id.root</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-21T15:05:18+00:00</t>
+    <t>2024-07-09T16:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2945" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2946" uniqueCount="532">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -866,7 +866,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1412: terminologyMaps using VF_LocationStatus on HOSPITAL LOCATION - SERVICE (44-9)</t>
+    <t>1412: source value from HOSPITAL LOCATION - SERVICE (44-9)</t>
   </si>
   <si>
     <t>Dim.Location.MedicalService,Dim.Location.MedicalService</t>
@@ -5402,11 +5402,13 @@
         <v>75</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="Y30" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z30" t="s" s="2">
-        <v>214</v>
+        <v>75</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>75</v>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -681,7 +681,7 @@
     <t>The status property covers the general availability of the resource, not the current value which may be covered by the operationStatus, or by a schedule/slots if they are configured for the location.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFLocationStatus</t>
+    <t>http://va.gov/fhir/ValueSet/LocationStatus</t>
   </si>
   <si>
     <t>1278: terminologyMaps using VF_LocationStatus</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1545,7 +1545,7 @@
     <t>Reference.display</t>
   </si>
   <si>
-    <t>1283: fixed value = Veterans Administration</t>
+    <t>1283: fixed value = "Veterans Administration"</t>
   </si>
   <si>
     <t>Location.partOf</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file HOSPITAL LOCATION (44) to us-core-location</t>
+    <t>This StructureDefinition contains the maps for VistA file HOSPITAL LOCATION (44) to us-core-location.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$112</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2946" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4066" uniqueCount="603">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -818,6 +818,10 @@
     <t>http://terminology.hl7.org/ValueSet/v3-ServiceDeliveryLocationRoleType</t>
   </si>
   <si>
+    <t xml:space="preserve">value:$this}
+</t>
+  </si>
+  <si>
     <t>.code</t>
   </si>
   <si>
@@ -848,6 +852,124 @@
     <t>union(., ./translation)</t>
   </si>
   <si>
+    <t>Location.type.coding.id</t>
+  </si>
+  <si>
+    <t>Location.type.coding.extension</t>
+  </si>
+  <si>
+    <t>Location.type.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://va.gov/terminology/VistADefinedTerms/44-9</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>1412-1: fixed value = http://va.gov/terminology/VistADefinedTerms/44-9</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>Location.type.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Location.type.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>1412: source value from HOSPITAL LOCATION - SERVICE (44-9)</t>
+  </si>
+  <si>
+    <t>Dim.Location.MedicalService,Dim.Location.MedicalService</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>Location.type.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>Location.type.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
     <t>Location.type.text</t>
   </si>
   <si>
@@ -866,13 +988,109 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1412: source value from HOSPITAL LOCATION - SERVICE (44-9)</t>
-  </si>
-  <si>
-    <t>Dim.Location.MedicalService,Dim.Location.MedicalService</t>
-  </si>
-  <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>Location.type:va-stop-code</t>
+  </si>
+  <si>
+    <t>va-stop-code</t>
+  </si>
+  <si>
+    <t>Location.type:va-stop-code.id</t>
+  </si>
+  <si>
+    <t>Location.type:va-stop-code.extension</t>
+  </si>
+  <si>
+    <t>Location.type:va-stop-code.coding</t>
+  </si>
+  <si>
+    <t>Location.type:va-stop-code.coding.id</t>
+  </si>
+  <si>
+    <t>Location.type:va-stop-code.coding.extension</t>
+  </si>
+  <si>
+    <t>Location.type:va-stop-code.coding.system</t>
+  </si>
+  <si>
+    <t>http://va.gov/terminology/VistADefinedTerms/44-8</t>
+  </si>
+  <si>
+    <t>2039-1: fixed value = http://va.gov/terminology/VistADefinedTerms/44-8</t>
+  </si>
+  <si>
+    <t>Location.type:va-stop-code.coding.version</t>
+  </si>
+  <si>
+    <t>Location.type:va-stop-code.coding.code</t>
+  </si>
+  <si>
+    <t>2039: source value from HOSPITAL LOCATION - STOP CODE NUMBER (44-8)</t>
+  </si>
+  <si>
+    <t>Dim.Location.PrimaryStopCodeIEN</t>
+  </si>
+  <si>
+    <t>Location.type:va-stop-code.coding.display</t>
+  </si>
+  <si>
+    <t>Location.type:va-stop-code.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Location.type:va-stop-code.text</t>
+  </si>
+  <si>
+    <t>Location.type:va-credit-code</t>
+  </si>
+  <si>
+    <t>va-credit-code</t>
+  </si>
+  <si>
+    <t>Location.type:va-credit-code.id</t>
+  </si>
+  <si>
+    <t>Location.type:va-credit-code.extension</t>
+  </si>
+  <si>
+    <t>Location.type:va-credit-code.coding</t>
+  </si>
+  <si>
+    <t>Location.type:va-credit-code.coding.id</t>
+  </si>
+  <si>
+    <t>Location.type:va-credit-code.coding.extension</t>
+  </si>
+  <si>
+    <t>Location.type:va-credit-code.coding.system</t>
+  </si>
+  <si>
+    <t>http://va.gov/terminology/VistADefinedTerms/44-2503</t>
+  </si>
+  <si>
+    <t>2040-1: fixed value = http://va.gov/terminology/VistADefinedTerms/44-2503</t>
+  </si>
+  <si>
+    <t>Location.type:va-credit-code.coding.version</t>
+  </si>
+  <si>
+    <t>Location.type:va-credit-code.coding.code</t>
+  </si>
+  <si>
+    <t>2040: source value from HOSPITAL LOCATION - CREDIT STOP CODE (44-2503)</t>
+  </si>
+  <si>
+    <t>Dim.Location.SecondaryStopCodeIEN</t>
+  </si>
+  <si>
+    <t>Location.type:va-credit-code.coding.display</t>
+  </si>
+  <si>
+    <t>Location.type:va-credit-code.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Location.type:va-credit-code.text</t>
   </si>
   <si>
     <t>Location.telecom</t>
@@ -1608,10 +1826,6 @@
   </si>
   <si>
     <t>Location.hoursOfOperation.allDay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
   </si>
   <si>
     <t>The Location is open all day</t>
@@ -1981,12 +2195,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN81"/>
+  <dimension ref="A1:AN112"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="42.98046875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="46.6015625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="42.98046875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="14.27734375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -4956,16 +5170,14 @@
         <v>75</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="AC26" s="2"/>
       <c r="AD26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>75</v>
+        <v>158</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>255</v>
@@ -4989,7 +5201,7 @@
         <v>75</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>254</v>
@@ -4997,10 +5209,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5109,10 +5321,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5223,10 +5435,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5252,16 +5464,16 @@
         <v>219</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>75</v>
@@ -5310,7 +5522,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -5331,7 +5543,7 @@
         <v>75</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>75</v>
@@ -5339,10 +5551,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5356,29 +5568,25 @@
         <v>84</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K30" t="s" s="2">
         <v>149</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>270</v>
+        <v>150</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>75</v>
       </c>
@@ -5426,7 +5634,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>274</v>
+        <v>152</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -5438,16 +5646,16 @@
         <v>75</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>275</v>
+        <v>75</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>276</v>
+        <v>75</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>277</v>
+        <v>153</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>75</v>
@@ -5455,14 +5663,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5472,7 +5680,7 @@
         <v>77</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>75</v>
@@ -5481,15 +5689,17 @@
         <v>75</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>279</v>
+        <v>130</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>280</v>
+        <v>131</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>133</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>75</v>
@@ -5526,19 +5736,19 @@
         <v>75</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>75</v>
+        <v>156</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>75</v>
+        <v>157</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>75</v>
+        <v>158</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>278</v>
+        <v>159</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -5550,7 +5760,7 @@
         <v>75</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>75</v>
@@ -5559,7 +5769,7 @@
         <v>75</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>282</v>
+        <v>153</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>75</v>
@@ -5567,10 +5777,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5584,25 +5794,29 @@
         <v>84</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>149</v>
+        <v>98</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>150</v>
+        <v>273</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>276</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>75</v>
       </c>
@@ -5611,7 +5825,7 @@
         <v>75</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>75</v>
+        <v>277</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>75</v>
@@ -5650,7 +5864,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>152</v>
+        <v>278</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -5662,16 +5876,16 @@
         <v>75</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>75</v>
+        <v>279</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>153</v>
+        <v>280</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>75</v>
@@ -5679,21 +5893,21 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>129</v>
+        <v>75</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>75</v>
@@ -5702,19 +5916,19 @@
         <v>75</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>131</v>
+        <v>282</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>155</v>
+        <v>283</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>133</v>
+        <v>284</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5752,31 +5966,31 @@
         <v>75</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>156</v>
+        <v>75</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>157</v>
+        <v>75</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>158</v>
+        <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>159</v>
+        <v>285</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>75</v>
@@ -5785,7 +5999,7 @@
         <v>75</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>153</v>
+        <v>286</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>75</v>
@@ -5793,10 +6007,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5822,13 +6036,15 @@
         <v>104</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+      <c r="O34" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>75</v>
       </c>
@@ -5837,7 +6053,7 @@
         <v>75</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>288</v>
+        <v>75</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>75</v>
@@ -5852,13 +6068,13 @@
         <v>75</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>165</v>
+        <v>75</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>289</v>
+        <v>75</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>290</v>
+        <v>75</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>75</v>
@@ -5885,16 +6101,16 @@
         <v>84</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>292</v>
+        <v>75</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AL34" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>294</v>
@@ -5922,7 +6138,7 @@
         <v>84</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>75</v>
@@ -5939,11 +6155,9 @@
       <c r="M35" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="N35" s="2"/>
+      <c r="O35" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>75</v>
@@ -5992,7 +6206,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -6007,13 +6221,13 @@
         <v>96</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>301</v>
+        <v>75</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>302</v>
+        <v>75</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>75</v>
@@ -6021,10 +6235,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6038,28 +6252,28 @@
         <v>84</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J36" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>104</v>
+        <v>302</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="N36" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>75</v>
@@ -6069,7 +6283,7 @@
         <v>75</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>309</v>
+        <v>75</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>75</v>
@@ -6084,13 +6298,13 @@
         <v>75</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>165</v>
+        <v>75</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>310</v>
+        <v>75</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>311</v>
+        <v>75</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>75</v>
@@ -6108,7 +6322,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -6123,13 +6337,13 @@
         <v>96</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>313</v>
+        <v>75</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>75</v>
@@ -6137,10 +6351,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6163,18 +6377,20 @@
         <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>316</v>
+        <v>149</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>75</v>
       </c>
@@ -6222,7 +6438,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -6243,7 +6459,7 @@
         <v>75</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>153</v>
+        <v>315</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>75</v>
@@ -6251,12 +6467,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="C38" s="2"/>
+        <v>255</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="D38" t="s" s="2">
         <v>75</v>
       </c>
@@ -6277,13 +6495,13 @@
         <v>85</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>199</v>
+        <v>171</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>322</v>
+        <v>256</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>323</v>
+        <v>257</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6310,13 +6528,13 @@
         <v>75</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>75</v>
+        <v>176</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>75</v>
+        <v>257</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>75</v>
+        <v>258</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>75</v>
@@ -6334,13 +6552,13 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>324</v>
+        <v>255</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>75</v>
@@ -6355,18 +6573,18 @@
         <v>75</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>325</v>
+        <v>260</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>75</v>
+        <v>254</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>326</v>
+        <v>261</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6380,7 +6598,7 @@
         <v>84</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>75</v>
@@ -6389,20 +6607,16 @@
         <v>75</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>327</v>
+        <v>149</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>328</v>
+        <v>150</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>331</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>75</v>
       </c>
@@ -6450,7 +6664,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>326</v>
+        <v>152</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -6462,7 +6676,7 @@
         <v>75</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>75</v>
@@ -6471,7 +6685,7 @@
         <v>75</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>332</v>
+        <v>153</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>75</v>
@@ -6479,21 +6693,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>333</v>
+        <v>262</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>75</v>
@@ -6505,15 +6719,17 @@
         <v>75</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>133</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>75</v>
@@ -6550,31 +6766,31 @@
         <v>75</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>75</v>
+        <v>156</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>75</v>
+        <v>157</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>75</v>
+        <v>158</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>75</v>
+        <v>135</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>75</v>
@@ -6591,14 +6807,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>334</v>
+        <v>263</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>129</v>
+        <v>75</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6614,21 +6830,23 @@
         <v>75</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>130</v>
+        <v>219</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>131</v>
+        <v>264</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>155</v>
+        <v>265</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>75</v>
       </c>
@@ -6664,19 +6882,19 @@
         <v>75</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>156</v>
+        <v>75</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>157</v>
+        <v>75</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>158</v>
+        <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>159</v>
+        <v>268</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -6688,7 +6906,7 @@
         <v>75</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>75</v>
@@ -6697,7 +6915,7 @@
         <v>75</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>153</v>
+        <v>269</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>75</v>
@@ -6705,10 +6923,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>335</v>
+        <v>270</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6725,26 +6943,22 @@
         <v>75</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>104</v>
+        <v>149</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>336</v>
+        <v>150</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>339</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>75</v>
       </c>
@@ -6756,7 +6970,7 @@
         <v>75</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>340</v>
+        <v>75</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>75</v>
@@ -6768,13 +6982,13 @@
         <v>75</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>165</v>
+        <v>75</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>341</v>
+        <v>75</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>342</v>
+        <v>75</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>75</v>
@@ -6792,7 +7006,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>343</v>
+        <v>152</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -6804,7 +7018,7 @@
         <v>75</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>75</v>
@@ -6813,7 +7027,7 @@
         <v>75</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>314</v>
+        <v>153</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>75</v>
@@ -6821,42 +7035,42 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>344</v>
+        <v>322</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>344</v>
+        <v>271</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>345</v>
+        <v>131</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>346</v>
+        <v>155</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>347</v>
+        <v>133</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6867,10 +7081,10 @@
         <v>75</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>348</v>
+        <v>75</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>349</v>
+        <v>75</v>
       </c>
       <c r="U43" t="s" s="2">
         <v>75</v>
@@ -6882,52 +7096,52 @@
         <v>75</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>165</v>
+        <v>75</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>350</v>
+        <v>75</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>351</v>
+        <v>75</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>75</v>
+        <v>156</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>75</v>
+        <v>157</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>75</v>
+        <v>158</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>352</v>
+        <v>159</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>353</v>
+        <v>75</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>354</v>
+        <v>75</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>314</v>
+        <v>153</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>75</v>
@@ -6935,10 +7149,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>355</v>
+        <v>323</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>355</v>
+        <v>272</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6961,19 +7175,19 @@
         <v>85</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>149</v>
+        <v>98</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>356</v>
+        <v>273</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>357</v>
+        <v>274</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>358</v>
+        <v>275</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>359</v>
+        <v>276</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>75</v>
@@ -6983,10 +7197,10 @@
         <v>75</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>75</v>
+        <v>324</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>360</v>
+        <v>75</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>75</v>
@@ -7022,7 +7236,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>361</v>
+        <v>278</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -7037,13 +7251,13 @@
         <v>96</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>75</v>
+        <v>325</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>362</v>
+        <v>280</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>75</v>
@@ -7051,10 +7265,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>363</v>
+        <v>326</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>363</v>
+        <v>281</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7065,10 +7279,10 @@
         <v>76</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>75</v>
@@ -7080,12 +7294,14 @@
         <v>149</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>364</v>
+        <v>282</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>75</v>
@@ -7098,7 +7314,7 @@
         <v>75</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>366</v>
+        <v>75</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>75</v>
@@ -7134,13 +7350,13 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>367</v>
+        <v>285</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>75</v>
@@ -7149,13 +7365,13 @@
         <v>96</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>368</v>
+        <v>75</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>369</v>
+        <v>75</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>370</v>
+        <v>286</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>75</v>
@@ -7163,14 +7379,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>371</v>
+        <v>327</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>371</v>
+        <v>287</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>372</v>
+        <v>75</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7180,7 +7396,7 @@
         <v>84</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>75</v>
@@ -7189,16 +7405,18 @@
         <v>85</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>149</v>
+        <v>104</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>373</v>
+        <v>288</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>374</v>
+        <v>289</v>
       </c>
       <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>75</v>
       </c>
@@ -7210,7 +7428,7 @@
         <v>75</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>375</v>
+        <v>75</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>75</v>
@@ -7246,7 +7464,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>376</v>
+        <v>291</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -7261,13 +7479,13 @@
         <v>96</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>377</v>
+        <v>328</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>378</v>
+        <v>329</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>379</v>
+        <v>294</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>75</v>
@@ -7275,14 +7493,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>380</v>
+        <v>330</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>380</v>
+        <v>295</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>381</v>
+        <v>75</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7292,7 +7510,7 @@
         <v>84</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>75</v>
@@ -7304,15 +7522,15 @@
         <v>149</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>382</v>
+        <v>296</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>75</v>
       </c>
@@ -7324,7 +7542,7 @@
         <v>75</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>385</v>
+        <v>75</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>75</v>
@@ -7360,7 +7578,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>386</v>
+        <v>299</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -7375,13 +7593,13 @@
         <v>96</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>387</v>
+        <v>75</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>388</v>
+        <v>75</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>389</v>
+        <v>300</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>75</v>
@@ -7389,14 +7607,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>390</v>
+        <v>331</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>390</v>
+        <v>301</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>391</v>
+        <v>75</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7406,7 +7624,7 @@
         <v>84</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>75</v>
@@ -7415,16 +7633,20 @@
         <v>85</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>149</v>
+        <v>302</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>392</v>
+        <v>303</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>75</v>
       </c>
@@ -7448,13 +7670,13 @@
         <v>75</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>176</v>
+        <v>75</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>394</v>
+        <v>75</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>395</v>
+        <v>75</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>75</v>
@@ -7472,7 +7694,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>396</v>
+        <v>307</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -7487,13 +7709,13 @@
         <v>96</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>397</v>
+        <v>75</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>354</v>
+        <v>75</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>398</v>
+        <v>308</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>75</v>
@@ -7501,14 +7723,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>399</v>
+        <v>332</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>399</v>
+        <v>309</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>400</v>
+        <v>75</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7518,7 +7740,7 @@
         <v>84</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>75</v>
@@ -7530,13 +7752,17 @@
         <v>149</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>401</v>
+        <v>310</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+        <v>311</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>75</v>
       </c>
@@ -7548,7 +7774,7 @@
         <v>75</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>403</v>
+        <v>75</v>
       </c>
       <c r="U49" t="s" s="2">
         <v>75</v>
@@ -7584,7 +7810,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>404</v>
+        <v>314</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -7599,13 +7825,13 @@
         <v>96</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>405</v>
+        <v>75</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>406</v>
+        <v>75</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>407</v>
+        <v>315</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>75</v>
@@ -7613,12 +7839,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>408</v>
+        <v>333</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="C50" s="2"/>
+        <v>255</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="D50" t="s" s="2">
         <v>75</v>
       </c>
@@ -7630,7 +7858,7 @@
         <v>84</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>75</v>
@@ -7639,17 +7867,15 @@
         <v>85</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>409</v>
+        <v>256</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>411</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>75</v>
@@ -7674,13 +7900,13 @@
         <v>75</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>75</v>
+        <v>176</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>75</v>
+        <v>257</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>75</v>
+        <v>258</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>75</v>
@@ -7698,13 +7924,13 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>412</v>
+        <v>255</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>75</v>
@@ -7713,24 +7939,24 @@
         <v>96</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>413</v>
+        <v>75</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>354</v>
+        <v>75</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>414</v>
+        <v>260</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>75</v>
+        <v>254</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>415</v>
+        <v>335</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>415</v>
+        <v>261</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7750,21 +7976,19 @@
         <v>75</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>199</v>
+        <v>149</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>416</v>
+        <v>150</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>417</v>
+        <v>151</v>
       </c>
       <c r="N51" s="2"/>
-      <c r="O51" t="s" s="2">
-        <v>418</v>
-      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>75</v>
       </c>
@@ -7776,7 +8000,7 @@
         <v>75</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>419</v>
+        <v>75</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>75</v>
@@ -7812,7 +8036,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>420</v>
+        <v>152</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -7824,7 +8048,7 @@
         <v>75</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>75</v>
@@ -7833,7 +8057,7 @@
         <v>75</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>325</v>
+        <v>153</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>75</v>
@@ -7841,21 +8065,21 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>421</v>
+        <v>336</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>421</v>
+        <v>262</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>75</v>
@@ -7864,21 +8088,21 @@
         <v>75</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>171</v>
+        <v>130</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>422</v>
+        <v>131</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>75</v>
       </c>
@@ -7902,43 +8126,43 @@
         <v>75</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>425</v>
+        <v>75</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>426</v>
+        <v>75</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>427</v>
+        <v>75</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>75</v>
+        <v>156</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>75</v>
+        <v>157</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>75</v>
+        <v>158</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>421</v>
+        <v>159</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>75</v>
@@ -7947,18 +8171,18 @@
         <v>75</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>428</v>
+        <v>153</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>254</v>
+        <v>75</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>429</v>
+        <v>337</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>429</v>
+        <v>263</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7969,7 +8193,7 @@
         <v>76</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>75</v>
@@ -7978,19 +8202,23 @@
         <v>75</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>149</v>
+        <v>219</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>150</v>
+        <v>264</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>75</v>
       </c>
@@ -8038,19 +8266,19 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>152</v>
+        <v>268</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>75</v>
@@ -8059,7 +8287,7 @@
         <v>75</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>153</v>
+        <v>269</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>75</v>
@@ -8067,21 +8295,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>430</v>
+        <v>338</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>430</v>
+        <v>270</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>129</v>
+        <v>75</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>75</v>
@@ -8093,17 +8321,15 @@
         <v>75</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>133</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>75</v>
@@ -8140,31 +8366,31 @@
         <v>75</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>156</v>
+        <v>75</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>157</v>
+        <v>75</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>158</v>
+        <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>75</v>
@@ -8181,14 +8407,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>431</v>
+        <v>339</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>431</v>
+        <v>271</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8204,23 +8430,21 @@
         <v>75</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>219</v>
+        <v>130</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>263</v>
+        <v>131</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>264</v>
+        <v>155</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>266</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>75</v>
       </c>
@@ -8256,19 +8480,19 @@
         <v>75</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>75</v>
+        <v>156</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>75</v>
+        <v>157</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>75</v>
+        <v>158</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>267</v>
+        <v>159</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -8280,7 +8504,7 @@
         <v>75</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>75</v>
@@ -8289,7 +8513,7 @@
         <v>75</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>268</v>
+        <v>153</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>75</v>
@@ -8297,10 +8521,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>432</v>
+        <v>340</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>432</v>
+        <v>272</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8314,7 +8538,7 @@
         <v>84</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>75</v>
@@ -8323,19 +8547,19 @@
         <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>149</v>
+        <v>98</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>75</v>
@@ -8345,7 +8569,7 @@
         <v>75</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>75</v>
+        <v>341</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>75</v>
@@ -8384,7 +8608,7 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -8399,13 +8623,13 @@
         <v>96</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>433</v>
+        <v>342</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>434</v>
+        <v>75</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>75</v>
@@ -8413,10 +8637,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>435</v>
+        <v>343</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>435</v>
+        <v>281</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8436,21 +8660,21 @@
         <v>75</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>436</v>
+        <v>149</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>437</v>
+        <v>282</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" t="s" s="2">
-        <v>439</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>75</v>
       </c>
@@ -8498,7 +8722,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>435</v>
+        <v>285</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -8519,7 +8743,7 @@
         <v>75</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>440</v>
+        <v>286</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>75</v>
@@ -8527,10 +8751,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>441</v>
+        <v>344</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>441</v>
+        <v>287</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8550,19 +8774,21 @@
         <v>75</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>149</v>
+        <v>104</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>150</v>
+        <v>288</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>151</v>
+        <v>289</v>
       </c>
       <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+      <c r="O58" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>75</v>
       </c>
@@ -8610,7 +8836,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>152</v>
+        <v>291</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -8622,16 +8848,16 @@
         <v>75</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>75</v>
+        <v>345</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>75</v>
+        <v>346</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>153</v>
+        <v>294</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>75</v>
@@ -8639,21 +8865,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>442</v>
+        <v>347</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>442</v>
+        <v>295</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>129</v>
+        <v>75</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>75</v>
@@ -8662,21 +8888,21 @@
         <v>75</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>131</v>
+        <v>296</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>75</v>
       </c>
@@ -8724,19 +8950,19 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>159</v>
+        <v>299</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>75</v>
@@ -8745,7 +8971,7 @@
         <v>75</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>153</v>
+        <v>300</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>75</v>
@@ -8753,45 +8979,45 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>443</v>
+        <v>348</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>443</v>
+        <v>301</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>444</v>
+        <v>75</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J60" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>130</v>
+        <v>302</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>445</v>
+        <v>303</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>446</v>
+        <v>304</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>133</v>
+        <v>305</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>139</v>
+        <v>306</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>75</v>
@@ -8840,19 +9066,19 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>447</v>
+        <v>307</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>75</v>
@@ -8861,7 +9087,7 @@
         <v>75</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>127</v>
+        <v>308</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>75</v>
@@ -8869,10 +9095,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>448</v>
+        <v>349</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>448</v>
+        <v>309</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8880,7 +9106,7 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>84</v>
@@ -8892,19 +9118,23 @@
         <v>75</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>449</v>
+        <v>149</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>450</v>
+        <v>310</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+        <v>311</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>75</v>
       </c>
@@ -8952,10 +9182,10 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>448</v>
+        <v>314</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>84</v>
@@ -8973,7 +9203,7 @@
         <v>75</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>452</v>
+        <v>315</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>75</v>
@@ -8981,10 +9211,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>453</v>
+        <v>350</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>453</v>
+        <v>350</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8992,13 +9222,13 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>75</v>
@@ -9007,13 +9237,13 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>449</v>
+        <v>351</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>454</v>
+        <v>352</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>455</v>
+        <v>353</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9064,13 +9294,13 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>453</v>
+        <v>350</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>75</v>
@@ -9085,7 +9315,7 @@
         <v>75</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>452</v>
+        <v>354</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>75</v>
@@ -9093,10 +9323,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>456</v>
+        <v>355</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>456</v>
+        <v>355</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9119,13 +9349,13 @@
         <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>449</v>
+        <v>149</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>457</v>
+        <v>150</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>458</v>
+        <v>151</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9176,7 +9406,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>456</v>
+        <v>152</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -9188,7 +9418,7 @@
         <v>75</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>75</v>
@@ -9197,7 +9427,7 @@
         <v>75</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>452</v>
+        <v>153</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>75</v>
@@ -9205,46 +9435,44 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>459</v>
+        <v>356</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>459</v>
+        <v>356</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>460</v>
+        <v>130</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>461</v>
+        <v>131</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>462</v>
+        <v>155</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>464</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>75</v>
       </c>
@@ -9280,31 +9508,31 @@
         <v>75</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>75</v>
+        <v>156</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>75</v>
+        <v>157</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>75</v>
+        <v>158</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>459</v>
+        <v>159</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>75</v>
@@ -9313,7 +9541,7 @@
         <v>75</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>465</v>
+        <v>153</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>75</v>
@@ -9321,10 +9549,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>466</v>
+        <v>357</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>466</v>
+        <v>357</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9338,22 +9566,22 @@
         <v>84</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>149</v>
+        <v>104</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>150</v>
+        <v>358</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>151</v>
+        <v>359</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9365,7 +9593,7 @@
         <v>75</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>75</v>
+        <v>360</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>75</v>
@@ -9380,13 +9608,13 @@
         <v>75</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>75</v>
+        <v>165</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>75</v>
+        <v>361</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>75</v>
+        <v>362</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>75</v>
@@ -9404,7 +9632,7 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>152</v>
+        <v>363</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -9413,19 +9641,19 @@
         <v>84</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>75</v>
+        <v>364</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>75</v>
+        <v>365</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>153</v>
+        <v>366</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>75</v>
@@ -9433,44 +9661,46 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>467</v>
+        <v>367</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>467</v>
+        <v>367</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>129</v>
+        <v>75</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>131</v>
+        <v>368</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>155</v>
+        <v>369</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="O66" s="2"/>
+        <v>370</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>371</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>75</v>
       </c>
@@ -9506,40 +9736,40 @@
         <v>75</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>156</v>
+        <v>75</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>157</v>
+        <v>75</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>158</v>
+        <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>159</v>
+        <v>372</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>75</v>
+        <v>373</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>75</v>
+        <v>374</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>153</v>
+        <v>375</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>75</v>
@@ -9547,10 +9777,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>468</v>
+        <v>376</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>468</v>
+        <v>376</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9564,27 +9794,29 @@
         <v>84</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J67" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>149</v>
+        <v>104</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>469</v>
+        <v>377</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>470</v>
+        <v>378</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="O67" s="2"/>
+        <v>379</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>380</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>75</v>
       </c>
@@ -9593,7 +9825,7 @@
         <v>75</v>
       </c>
       <c r="S67" t="s" s="2">
-        <v>75</v>
+        <v>381</v>
       </c>
       <c r="T67" t="s" s="2">
         <v>75</v>
@@ -9608,13 +9840,13 @@
         <v>75</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>75</v>
+        <v>165</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>75</v>
+        <v>382</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>75</v>
+        <v>383</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>75</v>
@@ -9632,7 +9864,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>472</v>
+        <v>384</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -9641,19 +9873,19 @@
         <v>84</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>473</v>
+        <v>75</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>75</v>
+        <v>385</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>127</v>
+        <v>386</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>75</v>
@@ -9661,10 +9893,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>474</v>
+        <v>387</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>474</v>
+        <v>387</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9687,16 +9919,16 @@
         <v>85</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>98</v>
+        <v>388</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>475</v>
+        <v>389</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>476</v>
+        <v>390</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>477</v>
+        <v>391</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9722,13 +9954,13 @@
         <v>75</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>176</v>
+        <v>75</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>478</v>
+        <v>75</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>479</v>
+        <v>75</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>75</v>
@@ -9746,7 +9978,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>480</v>
+        <v>392</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -9767,7 +9999,7 @@
         <v>75</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>75</v>
@@ -9775,10 +10007,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>481</v>
+        <v>393</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>481</v>
+        <v>393</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9801,17 +10033,15 @@
         <v>85</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>142</v>
+        <v>199</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>482</v>
+        <v>394</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>484</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>75</v>
@@ -9860,7 +10090,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>485</v>
+        <v>396</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -9881,7 +10111,7 @@
         <v>75</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>486</v>
+        <v>397</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>75</v>
@@ -9889,10 +10119,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>487</v>
+        <v>398</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>487</v>
+        <v>398</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9912,21 +10142,23 @@
         <v>75</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>149</v>
+        <v>399</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>488</v>
+        <v>400</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>489</v>
+        <v>401</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="O70" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>403</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>75</v>
       </c>
@@ -9935,7 +10167,7 @@
         <v>75</v>
       </c>
       <c r="S70" t="s" s="2">
-        <v>491</v>
+        <v>75</v>
       </c>
       <c r="T70" t="s" s="2">
         <v>75</v>
@@ -9974,7 +10206,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>492</v>
+        <v>398</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -9989,13 +10221,13 @@
         <v>96</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>493</v>
+        <v>75</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>127</v>
+        <v>404</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>75</v>
@@ -10003,10 +10235,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>494</v>
+        <v>405</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>494</v>
+        <v>405</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10029,18 +10261,16 @@
         <v>75</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>495</v>
+        <v>149</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>496</v>
+        <v>150</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>497</v>
+        <v>151</v>
       </c>
       <c r="N71" s="2"/>
-      <c r="O71" t="s" s="2">
-        <v>498</v>
-      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>75</v>
       </c>
@@ -10088,7 +10318,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>494</v>
+        <v>152</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -10100,7 +10330,7 @@
         <v>75</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>75</v>
@@ -10109,7 +10339,7 @@
         <v>75</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>499</v>
+        <v>153</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>75</v>
@@ -10117,14 +10347,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>500</v>
+        <v>406</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>500</v>
+        <v>406</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10143,16 +10373,16 @@
         <v>75</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>436</v>
+        <v>130</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>501</v>
+        <v>131</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>502</v>
+        <v>155</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>503</v>
+        <v>133</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10190,19 +10420,19 @@
         <v>75</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>75</v>
+        <v>156</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>75</v>
+        <v>157</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>75</v>
+        <v>158</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>500</v>
+        <v>159</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
@@ -10214,7 +10444,7 @@
         <v>75</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>75</v>
@@ -10223,7 +10453,7 @@
         <v>75</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>504</v>
+        <v>153</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>75</v>
@@ -10231,10 +10461,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>505</v>
+        <v>407</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>505</v>
+        <v>407</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10251,22 +10481,26 @@
         <v>75</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>149</v>
+        <v>104</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>150</v>
+        <v>408</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
+        <v>409</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>411</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>75</v>
       </c>
@@ -10278,7 +10512,7 @@
         <v>75</v>
       </c>
       <c r="T73" t="s" s="2">
-        <v>75</v>
+        <v>412</v>
       </c>
       <c r="U73" t="s" s="2">
         <v>75</v>
@@ -10290,13 +10524,13 @@
         <v>75</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>75</v>
+        <v>165</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>75</v>
+        <v>413</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>75</v>
+        <v>414</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>75</v>
@@ -10314,7 +10548,7 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>152</v>
+        <v>415</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>76</v>
@@ -10326,7 +10560,7 @@
         <v>75</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>75</v>
@@ -10335,7 +10569,7 @@
         <v>75</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>153</v>
+        <v>386</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>75</v>
@@ -10343,42 +10577,42 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>506</v>
+        <v>416</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>506</v>
+        <v>416</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>129</v>
+        <v>75</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>131</v>
+        <v>417</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>155</v>
+        <v>418</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>133</v>
+        <v>419</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10389,10 +10623,10 @@
         <v>75</v>
       </c>
       <c r="S74" t="s" s="2">
-        <v>75</v>
+        <v>420</v>
       </c>
       <c r="T74" t="s" s="2">
-        <v>75</v>
+        <v>421</v>
       </c>
       <c r="U74" t="s" s="2">
         <v>75</v>
@@ -10404,13 +10638,13 @@
         <v>75</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>75</v>
+        <v>165</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>75</v>
+        <v>422</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>75</v>
+        <v>423</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>75</v>
@@ -10428,28 +10662,28 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>159</v>
+        <v>424</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>75</v>
+        <v>425</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>75</v>
+        <v>426</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>153</v>
+        <v>386</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>75</v>
@@ -10457,45 +10691,45 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>507</v>
+        <v>427</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>507</v>
+        <v>427</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>444</v>
+        <v>75</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J75" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>445</v>
+        <v>428</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>446</v>
+        <v>429</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>133</v>
+        <v>430</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>139</v>
+        <v>431</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>75</v>
@@ -10508,7 +10742,7 @@
         <v>75</v>
       </c>
       <c r="T75" t="s" s="2">
-        <v>75</v>
+        <v>432</v>
       </c>
       <c r="U75" t="s" s="2">
         <v>75</v>
@@ -10544,19 +10778,19 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>75</v>
@@ -10565,7 +10799,7 @@
         <v>75</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>127</v>
+        <v>434</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>75</v>
@@ -10573,10 +10807,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>508</v>
+        <v>435</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>508</v>
+        <v>435</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10590,22 +10824,22 @@
         <v>77</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>104</v>
+        <v>149</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>509</v>
+        <v>436</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>510</v>
+        <v>437</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10620,7 +10854,7 @@
         <v>75</v>
       </c>
       <c r="T76" t="s" s="2">
-        <v>75</v>
+        <v>438</v>
       </c>
       <c r="U76" t="s" s="2">
         <v>75</v>
@@ -10632,13 +10866,13 @@
         <v>75</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>165</v>
+        <v>75</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>511</v>
+        <v>75</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>512</v>
+        <v>75</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>75</v>
@@ -10656,7 +10890,7 @@
         <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>508</v>
+        <v>439</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -10671,13 +10905,13 @@
         <v>96</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>75</v>
+        <v>440</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>75</v>
+        <v>441</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>504</v>
+        <v>442</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>75</v>
@@ -10685,14 +10919,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>513</v>
+        <v>443</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>513</v>
+        <v>443</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>75</v>
+        <v>444</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -10702,22 +10936,22 @@
         <v>84</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>514</v>
+        <v>149</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>515</v>
+        <v>445</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>516</v>
+        <v>446</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10732,7 +10966,7 @@
         <v>75</v>
       </c>
       <c r="T77" t="s" s="2">
-        <v>75</v>
+        <v>447</v>
       </c>
       <c r="U77" t="s" s="2">
         <v>75</v>
@@ -10768,7 +11002,7 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>513</v>
+        <v>448</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
@@ -10783,13 +11017,13 @@
         <v>96</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>75</v>
+        <v>449</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>75</v>
+        <v>450</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>504</v>
+        <v>451</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>75</v>
@@ -10797,14 +11031,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>517</v>
+        <v>452</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>517</v>
+        <v>452</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>75</v>
+        <v>453</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -10814,24 +11048,26 @@
         <v>84</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>518</v>
+        <v>149</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>519</v>
+        <v>454</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>455</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>456</v>
+      </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>75</v>
@@ -10844,7 +11080,7 @@
         <v>75</v>
       </c>
       <c r="T78" t="s" s="2">
-        <v>75</v>
+        <v>457</v>
       </c>
       <c r="U78" t="s" s="2">
         <v>75</v>
@@ -10880,7 +11116,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>517</v>
+        <v>458</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
@@ -10895,13 +11131,13 @@
         <v>96</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>75</v>
+        <v>459</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>75</v>
+        <v>460</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>504</v>
+        <v>461</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>75</v>
@@ -10909,14 +11145,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>521</v>
+        <v>462</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>521</v>
+        <v>462</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>75</v>
+        <v>463</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -10926,22 +11162,22 @@
         <v>84</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>518</v>
+        <v>149</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>522</v>
+        <v>464</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>523</v>
+        <v>465</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -10968,13 +11204,13 @@
         <v>75</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>75</v>
+        <v>176</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>75</v>
+        <v>466</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>75</v>
+        <v>467</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>75</v>
@@ -10992,7 +11228,7 @@
         <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>521</v>
+        <v>468</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
@@ -11007,13 +11243,13 @@
         <v>96</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>75</v>
+        <v>469</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>75</v>
+        <v>426</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>504</v>
+        <v>470</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>75</v>
@@ -11021,14 +11257,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>524</v>
+        <v>471</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>524</v>
+        <v>471</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>75</v>
+        <v>472</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11038,22 +11274,22 @@
         <v>84</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K80" t="s" s="2">
         <v>149</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>525</v>
+        <v>473</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>526</v>
+        <v>474</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11068,7 +11304,7 @@
         <v>75</v>
       </c>
       <c r="T80" t="s" s="2">
-        <v>75</v>
+        <v>475</v>
       </c>
       <c r="U80" t="s" s="2">
         <v>75</v>
@@ -11104,7 +11340,7 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>524</v>
+        <v>476</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
@@ -11119,13 +11355,13 @@
         <v>96</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>75</v>
+        <v>477</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>75</v>
+        <v>478</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>153</v>
+        <v>479</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>75</v>
@@ -11133,10 +11369,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>527</v>
+        <v>480</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>527</v>
+        <v>480</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11147,30 +11383,30 @@
         <v>76</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>528</v>
+        <v>149</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>529</v>
+        <v>481</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" t="s" s="2">
-        <v>531</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>75</v>
       </c>
@@ -11218,13 +11454,13 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>527</v>
+        <v>484</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>75</v>
@@ -11233,20 +11469,3540 @@
         <v>96</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>75</v>
+        <v>485</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>75</v>
+        <v>426</v>
       </c>
       <c r="AM81" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="82" hidden="true">
+      <c r="A82" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="P82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="83" hidden="true">
+      <c r="A83" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="P83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="84" hidden="true">
+      <c r="A84" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
+      <c r="P84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM84" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AN81" t="s" s="2">
+      <c r="AN84" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="O85" s="2"/>
+      <c r="P85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="P86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="87" hidden="true">
+      <c r="A87" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="P87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="P88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="89" hidden="true">
+      <c r="A89" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="N89" s="2"/>
+      <c r="O89" s="2"/>
+      <c r="P89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="90" hidden="true">
+      <c r="A90" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="O90" s="2"/>
+      <c r="P90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="91" hidden="true">
+      <c r="A91" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="P91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
+      <c r="P92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="93" hidden="true">
+      <c r="A93" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="N93" s="2"/>
+      <c r="O93" s="2"/>
+      <c r="P93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="94" hidden="true">
+      <c r="A94" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="N94" s="2"/>
+      <c r="O94" s="2"/>
+      <c r="P94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="95" hidden="true">
+      <c r="A95" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="P95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="96" hidden="true">
+      <c r="A96" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
+      <c r="P96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="97" hidden="true">
+      <c r="A97" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="O97" s="2"/>
+      <c r="P97" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="O98" s="2"/>
+      <c r="P98" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="99" hidden="true">
+      <c r="A99" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="O99" s="2"/>
+      <c r="P99" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="100" hidden="true">
+      <c r="A100" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="O100" s="2"/>
+      <c r="P100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="101" hidden="true">
+      <c r="A101" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="O101" s="2"/>
+      <c r="P101" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="102" hidden="true">
+      <c r="A102" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="P102" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="103" hidden="true">
+      <c r="A103" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="O103" s="2"/>
+      <c r="P103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="104" hidden="true">
+      <c r="A104" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="N104" s="2"/>
+      <c r="O104" s="2"/>
+      <c r="P104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="105" hidden="true">
+      <c r="A105" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="O105" s="2"/>
+      <c r="P105" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="106" hidden="true">
+      <c r="A106" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="P106" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="107" hidden="true">
+      <c r="A107" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="N107" s="2"/>
+      <c r="O107" s="2"/>
+      <c r="P107" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q107" s="2"/>
+      <c r="R107" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="108" hidden="true">
+      <c r="A108" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E108" s="2"/>
+      <c r="F108" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="N108" s="2"/>
+      <c r="O108" s="2"/>
+      <c r="P108" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q108" s="2"/>
+      <c r="R108" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S108" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="109" hidden="true">
+      <c r="A109" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E109" s="2"/>
+      <c r="F109" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="N109" s="2"/>
+      <c r="O109" s="2"/>
+      <c r="P109" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q109" s="2"/>
+      <c r="R109" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S109" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF109" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="AG109" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="110" hidden="true">
+      <c r="A110" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="C110" s="2"/>
+      <c r="D110" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E110" s="2"/>
+      <c r="F110" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="N110" s="2"/>
+      <c r="O110" s="2"/>
+      <c r="P110" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q110" s="2"/>
+      <c r="R110" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S110" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF110" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="AG110" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI110" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL110" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AN110" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="111" hidden="true">
+      <c r="A111" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="C111" s="2"/>
+      <c r="D111" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E111" s="2"/>
+      <c r="F111" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="N111" s="2"/>
+      <c r="O111" s="2"/>
+      <c r="P111" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q111" s="2"/>
+      <c r="R111" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S111" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T111" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U111" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V111" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W111" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X111" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z111" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF111" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AG111" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI111" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK111" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AN111" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="112" hidden="true">
+      <c r="A112" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="C112" s="2"/>
+      <c r="D112" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E112" s="2"/>
+      <c r="F112" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="N112" s="2"/>
+      <c r="O112" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="P112" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q112" s="2"/>
+      <c r="R112" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S112" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM112" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AN112" t="s" s="2">
         <v>75</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN81">
+  <autoFilter ref="A1:AN112">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11256,7 +15012,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI80">
+  <conditionalFormatting sqref="A2:AI111">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -625,7 +625,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>755: source value from HOSPITAL LOCATION - IEN (44-.001)</t>
+    <t>755: source value based on HOSPITAL LOCATION - IEN (44-.001)</t>
   </si>
   <si>
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
@@ -724,7 +724,7 @@
     <t>If the name of a location changes, consider putting the old name in the alias column so that it can still be located through searches.</t>
   </si>
   <si>
-    <t>756: source value from HOSPITAL LOCATION - NAME (44-.01)</t>
+    <t>756: source value based on HOSPITAL LOCATION - NAME (44-.01)</t>
   </si>
   <si>
     <t>Dim.Location.LocationName,Dim.Location.LocationName</t>
@@ -749,7 +749,7 @@
 For searching knowing previous names that the location was known by can be very useful.</t>
   </si>
   <si>
-    <t>1277: source value from HOSPITAL LOCATION - SYNONYM (44-13)</t>
+    <t>1277: source value based on HOSPITAL LOCATION - SYNONYM (44-13)</t>
   </si>
   <si>
     <t>Dim.Location.LocationAbbreviation,Dim.Location.LocationAbbreviation</t>
@@ -767,7 +767,7 @@
     <t>Humans need additional information to verify a correct location has been identified.</t>
   </si>
   <si>
-    <t>1279: source value from HOSPITAL LOCATION - PATIENT FRIENDLY NAME (44-60)</t>
+    <t>1279: source value based on HOSPITAL LOCATION - PATIENT FRIENDLY NAME (44-60)</t>
   </si>
   <si>
     <t>Dim.Location.PatientFriendlyLocationName,Dim.Location.PatientFriendlyLocationName</t>
@@ -918,7 +918,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>1412: source value from HOSPITAL LOCATION - SERVICE (44-9)</t>
+    <t>1412: source value based on HOSPITAL LOCATION - SERVICE (44-9)</t>
   </si>
   <si>
     <t>Dim.Location.MedicalService,Dim.Location.MedicalService</t>
@@ -1027,7 +1027,7 @@
     <t>Location.type:va-stop-code.coding.code</t>
   </si>
   <si>
-    <t>2039: source value from HOSPITAL LOCATION - STOP CODE NUMBER (44-8)</t>
+    <t>2039: source value based on HOSPITAL LOCATION - STOP CODE NUMBER (44-8)</t>
   </si>
   <si>
     <t>Dim.Location.PrimaryStopCodeIEN</t>
@@ -1078,7 +1078,7 @@
     <t>Location.type:va-credit-code.coding.code</t>
   </si>
   <si>
-    <t>2040: source value from HOSPITAL LOCATION - CREDIT STOP CODE (44-2503)</t>
+    <t>2040: source value based on HOSPITAL LOCATION - CREDIT STOP CODE (44-2503)</t>
   </si>
   <si>
     <t>Dim.Location.SecondaryStopCodeIEN</t>
@@ -1367,7 +1367,7 @@
     <t>Address.line</t>
   </si>
   <si>
-    <t>1318: source value from HOSPITAL LOCATION - INSTITUTION &gt; INSTITUTION - STREET ADDR. 2 (44-3 &gt; 4-1.02)</t>
+    <t>1318: source value based on HOSPITAL LOCATION - INSTITUTION &gt; INSTITUTION - STREET ADDR. 2 (44-3 &gt; 4-1.02)</t>
   </si>
   <si>
     <t>Dim.Location.InstitutionIEN
@@ -1396,7 +1396,7 @@
     <t>Address.city</t>
   </si>
   <si>
-    <t>1319: source value from HOSPITAL LOCATION - INSTITUTION &gt; INSTITUTION - CITY (44-3 &gt; 4-1.03)</t>
+    <t>1319: source value based on HOSPITAL LOCATION - INSTITUTION &gt; INSTITUTION - CITY (44-3 &gt; 4-1.03)</t>
   </si>
   <si>
     <t>Dim.Location.InstitutionIEN
@@ -1428,7 +1428,7 @@
     <t>Address.district</t>
   </si>
   <si>
-    <t>1316: source value from HOSPITAL LOCATION - INSTITUTION &gt; INSTITUTION - DISTRICT (44-3 &gt; 4-.03)</t>
+    <t>1316: source value based on HOSPITAL LOCATION - INSTITUTION &gt; INSTITUTION - DISTRICT (44-3 &gt; 4-.03)</t>
   </si>
   <si>
     <t>Dim.Location.InstitutionIEN
@@ -1460,7 +1460,7 @@
     <t>Address.state</t>
   </si>
   <si>
-    <t>1315: source value from HOSPITAL LOCATION - INSTITUTION &gt; INSTITUTION - STATE &gt; STATE - ABBREVIATION (44-3 &gt; 4-.02 &gt; 5-1)</t>
+    <t>1315: source value based on HOSPITAL LOCATION - INSTITUTION &gt; INSTITUTION - STATE &gt; STATE - ABBREVIATION (44-3 &gt; 4-.02 &gt; 5-1)</t>
   </si>
   <si>
     <t>AD.part[parttype = STA]</t>
@@ -1485,7 +1485,7 @@
     <t>Address.postalCode</t>
   </si>
   <si>
-    <t>1320: source value from HOSPITAL LOCATION - INSTITUTION &gt; INSTITUTION - ZIP (44-3 &gt; 4-1.04)</t>
+    <t>1320: source value based on HOSPITAL LOCATION - INSTITUTION &gt; INSTITUTION - ZIP (44-3 &gt; 4-1.04)</t>
   </si>
   <si>
     <t>Dim.Location.InstitutionIEN
@@ -1510,7 +1510,7 @@
     <t>Address.country</t>
   </si>
   <si>
-    <t>1405: source value from HOSPITAL LOCATION - INSTITUTION &gt; INSTITUTION - COUNTRY &gt; COUNTRY CODE - CODE (44-3 &gt; 4-801 &gt; 779.004-.01)</t>
+    <t>1405: source value based on HOSPITAL LOCATION - INSTITUTION &gt; INSTITUTION - COUNTRY &gt; COUNTRY CODE - CODE (44-3 &gt; 4-801 &gt; 779.004-.01)</t>
   </si>
   <si>
     <t>AD.part[parttype = CNT]</t>
@@ -1573,7 +1573,7 @@
     <t>Location.physicalType.text</t>
   </si>
   <si>
-    <t>1284: source value from HOSPITAL LOCATION - PHYSICAL LOCATION (44-10)</t>
+    <t>1284: source value based on HOSPITAL LOCATION - PHYSICAL LOCATION (44-10)</t>
   </si>
   <si>
     <t>Dim.Location.PhysicalLocation,Dim.Location.PhysicalLocation</t>
@@ -2233,7 +2233,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="134.546875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="138.640625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="129.9609375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4066" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4067" uniqueCount="604">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -679,6 +679,9 @@
   </si>
   <si>
     <t>The status property covers the general availability of the resource, not the current value which may be covered by the operationStatus, or by a schedule/slots if they are configured for the location.</t>
+  </si>
+  <si>
+    <t>see mapping [VF_LocationStatus](ConceptMap-VF-LocationStatus.html)</t>
   </si>
   <si>
     <t>http://va.gov/fhir/ValueSet/LocationStatus</t>
@@ -4478,9 +4481,11 @@
       <c r="X20" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="Y20" s="2"/>
+      <c r="Y20" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="Z20" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>75</v>
@@ -4513,24 +4518,24 @@
         <v>96</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4553,13 +4558,13 @@
         <v>85</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4589,10 +4594,10 @@
         <v>108</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>75</v>
@@ -4610,7 +4615,7 @@
         <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -4634,15 +4639,15 @@
         <v>153</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4668,13 +4673,13 @@
         <v>149</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4724,7 +4729,7 @@
         <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -4739,13 +4744,13 @@
         <v>96</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>75</v>
@@ -4753,10 +4758,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4782,16 +4787,16 @@
         <v>149</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>75</v>
@@ -4840,7 +4845,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -4855,13 +4860,13 @@
         <v>96</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>75</v>
@@ -4869,10 +4874,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4898,14 +4903,14 @@
         <v>149</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>75</v>
@@ -4954,7 +4959,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -4969,13 +4974,13 @@
         <v>96</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>75</v>
@@ -4983,10 +4988,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5012,16 +5017,16 @@
         <v>104</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>75</v>
@@ -5031,7 +5036,7 @@
         <v>75</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>75</v>
@@ -5049,10 +5054,10 @@
         <v>165</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>75</v>
@@ -5070,7 +5075,7 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -5085,24 +5090,24 @@
         <v>96</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5128,10 +5133,10 @@
         <v>171</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5161,16 +5166,16 @@
         <v>176</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AC26" s="2"/>
       <c r="AD26" t="s" s="2">
@@ -5180,7 +5185,7 @@
         <v>158</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -5201,18 +5206,18 @@
         <v>75</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5321,10 +5326,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5435,10 +5440,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5461,19 +5466,19 @@
         <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>75</v>
@@ -5522,7 +5527,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -5543,7 +5548,7 @@
         <v>75</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>75</v>
@@ -5551,10 +5556,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5663,10 +5668,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5777,10 +5782,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5806,16 +5811,16 @@
         <v>98</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>75</v>
@@ -5825,7 +5830,7 @@
         <v>75</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>75</v>
@@ -5864,7 +5869,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -5879,13 +5884,13 @@
         <v>96</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>75</v>
@@ -5893,10 +5898,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5922,13 +5927,13 @@
         <v>149</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5978,7 +5983,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -5999,7 +6004,7 @@
         <v>75</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>75</v>
@@ -6007,10 +6012,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6036,14 +6041,14 @@
         <v>104</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>75</v>
@@ -6092,7 +6097,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -6107,13 +6112,13 @@
         <v>96</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>75</v>
@@ -6121,10 +6126,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6150,14 +6155,14 @@
         <v>149</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>75</v>
@@ -6206,7 +6211,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -6227,7 +6232,7 @@
         <v>75</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>75</v>
@@ -6235,10 +6240,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6261,19 +6266,19 @@
         <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>75</v>
@@ -6322,7 +6327,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -6343,7 +6348,7 @@
         <v>75</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>75</v>
@@ -6351,10 +6356,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6380,16 +6385,16 @@
         <v>149</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>75</v>
@@ -6438,7 +6443,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -6459,7 +6464,7 @@
         <v>75</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>75</v>
@@ -6467,13 +6472,13 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>75</v>
@@ -6498,10 +6503,10 @@
         <v>171</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6531,10 +6536,10 @@
         <v>176</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>75</v>
@@ -6552,7 +6557,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -6573,18 +6578,18 @@
         <v>75</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6693,10 +6698,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6807,10 +6812,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6833,19 +6838,19 @@
         <v>85</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>75</v>
@@ -6894,7 +6899,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -6915,7 +6920,7 @@
         <v>75</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>75</v>
@@ -6923,10 +6928,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7035,10 +7040,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7149,10 +7154,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7178,16 +7183,16 @@
         <v>98</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>75</v>
@@ -7197,7 +7202,7 @@
         <v>75</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>75</v>
@@ -7236,7 +7241,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -7251,13 +7256,13 @@
         <v>96</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>75</v>
@@ -7265,10 +7270,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7294,13 +7299,13 @@
         <v>149</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7350,7 +7355,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -7371,7 +7376,7 @@
         <v>75</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>75</v>
@@ -7379,10 +7384,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7408,14 +7413,14 @@
         <v>104</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>75</v>
@@ -7464,7 +7469,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -7479,13 +7484,13 @@
         <v>96</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>75</v>
@@ -7493,10 +7498,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7522,14 +7527,14 @@
         <v>149</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>75</v>
@@ -7578,7 +7583,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -7599,7 +7604,7 @@
         <v>75</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>75</v>
@@ -7607,10 +7612,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7633,19 +7638,19 @@
         <v>85</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>75</v>
@@ -7694,7 +7699,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -7715,7 +7720,7 @@
         <v>75</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>75</v>
@@ -7723,10 +7728,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7752,16 +7757,16 @@
         <v>149</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>75</v>
@@ -7810,7 +7815,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -7831,7 +7836,7 @@
         <v>75</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>75</v>
@@ -7839,13 +7844,13 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>75</v>
@@ -7870,10 +7875,10 @@
         <v>171</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7903,10 +7908,10 @@
         <v>176</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>75</v>
@@ -7924,7 +7929,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -7945,18 +7950,18 @@
         <v>75</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8065,10 +8070,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8179,10 +8184,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8205,19 +8210,19 @@
         <v>85</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>75</v>
@@ -8266,7 +8271,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -8287,7 +8292,7 @@
         <v>75</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>75</v>
@@ -8295,10 +8300,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8407,10 +8412,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8521,10 +8526,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8550,16 +8555,16 @@
         <v>98</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>75</v>
@@ -8569,7 +8574,7 @@
         <v>75</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>75</v>
@@ -8608,7 +8613,7 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -8623,13 +8628,13 @@
         <v>96</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>75</v>
@@ -8637,10 +8642,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8666,13 +8671,13 @@
         <v>149</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8722,7 +8727,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -8743,7 +8748,7 @@
         <v>75</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>75</v>
@@ -8751,10 +8756,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8780,14 +8785,14 @@
         <v>104</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>75</v>
@@ -8836,7 +8841,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -8851,13 +8856,13 @@
         <v>96</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>75</v>
@@ -8865,10 +8870,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8894,14 +8899,14 @@
         <v>149</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>75</v>
@@ -8950,7 +8955,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -8971,7 +8976,7 @@
         <v>75</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>75</v>
@@ -8979,10 +8984,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9005,19 +9010,19 @@
         <v>85</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>75</v>
@@ -9066,7 +9071,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -9087,7 +9092,7 @@
         <v>75</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>75</v>
@@ -9095,10 +9100,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9124,16 +9129,16 @@
         <v>149</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>75</v>
@@ -9182,7 +9187,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -9203,7 +9208,7 @@
         <v>75</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>75</v>
@@ -9211,10 +9216,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9237,13 +9242,13 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9294,7 +9299,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
@@ -9315,7 +9320,7 @@
         <v>75</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>75</v>
@@ -9323,10 +9328,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9435,10 +9440,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9549,10 +9554,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9578,10 +9583,10 @@
         <v>104</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9593,7 +9598,7 @@
         <v>75</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>75</v>
@@ -9611,10 +9616,10 @@
         <v>165</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>75</v>
@@ -9632,7 +9637,7 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -9641,19 +9646,19 @@
         <v>84</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>75</v>
@@ -9661,10 +9666,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9690,16 +9695,16 @@
         <v>149</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>75</v>
@@ -9748,7 +9753,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
@@ -9763,13 +9768,13 @@
         <v>96</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>75</v>
@@ -9777,10 +9782,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9806,16 +9811,16 @@
         <v>104</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>75</v>
@@ -9825,7 +9830,7 @@
         <v>75</v>
       </c>
       <c r="S67" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="T67" t="s" s="2">
         <v>75</v>
@@ -9843,10 +9848,10 @@
         <v>165</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>75</v>
@@ -9864,7 +9869,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -9879,13 +9884,13 @@
         <v>96</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>75</v>
@@ -9893,10 +9898,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9919,16 +9924,16 @@
         <v>85</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9978,7 +9983,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -10007,10 +10012,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10036,10 +10041,10 @@
         <v>199</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10090,7 +10095,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -10111,7 +10116,7 @@
         <v>75</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>75</v>
@@ -10119,10 +10124,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10145,19 +10150,19 @@
         <v>75</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>75</v>
@@ -10206,7 +10211,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -10227,7 +10232,7 @@
         <v>75</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>75</v>
@@ -10235,10 +10240,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10347,10 +10352,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10461,10 +10466,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10490,16 +10495,16 @@
         <v>104</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>75</v>
@@ -10512,7 +10517,7 @@
         <v>75</v>
       </c>
       <c r="T73" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="U73" t="s" s="2">
         <v>75</v>
@@ -10527,10 +10532,10 @@
         <v>165</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>75</v>
@@ -10548,7 +10553,7 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>76</v>
@@ -10569,7 +10574,7 @@
         <v>75</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>75</v>
@@ -10577,10 +10582,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10606,13 +10611,13 @@
         <v>104</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10623,10 +10628,10 @@
         <v>75</v>
       </c>
       <c r="S74" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="T74" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="U74" t="s" s="2">
         <v>75</v>
@@ -10641,10 +10646,10 @@
         <v>165</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>75</v>
@@ -10662,7 +10667,7 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>76</v>
@@ -10677,13 +10682,13 @@
         <v>96</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>75</v>
@@ -10691,10 +10696,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10720,16 +10725,16 @@
         <v>149</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>75</v>
@@ -10742,7 +10747,7 @@
         <v>75</v>
       </c>
       <c r="T75" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="U75" t="s" s="2">
         <v>75</v>
@@ -10778,7 +10783,7 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
@@ -10799,7 +10804,7 @@
         <v>75</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>75</v>
@@ -10807,10 +10812,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10836,10 +10841,10 @@
         <v>149</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10854,7 +10859,7 @@
         <v>75</v>
       </c>
       <c r="T76" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="U76" t="s" s="2">
         <v>75</v>
@@ -10890,7 +10895,7 @@
         <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -10905,13 +10910,13 @@
         <v>96</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>75</v>
@@ -10919,14 +10924,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -10948,10 +10953,10 @@
         <v>149</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10966,7 +10971,7 @@
         <v>75</v>
       </c>
       <c r="T77" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="U77" t="s" s="2">
         <v>75</v>
@@ -11002,7 +11007,7 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
@@ -11017,13 +11022,13 @@
         <v>96</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>75</v>
@@ -11031,14 +11036,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11060,13 +11065,13 @@
         <v>149</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11080,7 +11085,7 @@
         <v>75</v>
       </c>
       <c r="T78" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="U78" t="s" s="2">
         <v>75</v>
@@ -11116,7 +11121,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
@@ -11131,13 +11136,13 @@
         <v>96</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>75</v>
@@ -11145,14 +11150,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11174,10 +11179,10 @@
         <v>149</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11207,10 +11212,10 @@
         <v>176</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>75</v>
@@ -11228,7 +11233,7 @@
         <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
@@ -11243,13 +11248,13 @@
         <v>96</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>75</v>
@@ -11257,14 +11262,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11286,10 +11291,10 @@
         <v>149</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11304,7 +11309,7 @@
         <v>75</v>
       </c>
       <c r="T80" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="U80" t="s" s="2">
         <v>75</v>
@@ -11340,7 +11345,7 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
@@ -11355,13 +11360,13 @@
         <v>96</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>75</v>
@@ -11369,10 +11374,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11398,13 +11403,13 @@
         <v>149</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11454,7 +11459,7 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>
@@ -11469,13 +11474,13 @@
         <v>96</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>75</v>
@@ -11483,10 +11488,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11512,14 +11517,14 @@
         <v>199</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>75</v>
@@ -11532,7 +11537,7 @@
         <v>75</v>
       </c>
       <c r="T82" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="U82" t="s" s="2">
         <v>75</v>
@@ -11568,7 +11573,7 @@
         <v>75</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>76</v>
@@ -11589,7 +11594,7 @@
         <v>75</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>75</v>
@@ -11597,10 +11602,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11626,14 +11631,14 @@
         <v>171</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>75</v>
@@ -11658,13 +11663,13 @@
         <v>75</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>75</v>
@@ -11682,7 +11687,7 @@
         <v>75</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>76</v>
@@ -11703,18 +11708,18 @@
         <v>75</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11823,10 +11828,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11937,10 +11942,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11963,19 +11968,19 @@
         <v>85</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>75</v>
@@ -12024,7 +12029,7 @@
         <v>75</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>76</v>
@@ -12045,7 +12050,7 @@
         <v>75</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>75</v>
@@ -12053,10 +12058,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12082,16 +12087,16 @@
         <v>149</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>75</v>
@@ -12140,7 +12145,7 @@
         <v>75</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>76</v>
@@ -12155,13 +12160,13 @@
         <v>96</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>75</v>
@@ -12169,10 +12174,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12195,17 +12200,17 @@
         <v>75</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>75</v>
@@ -12254,7 +12259,7 @@
         <v>75</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>76</v>
@@ -12275,7 +12280,7 @@
         <v>75</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>75</v>
@@ -12283,10 +12288,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12395,10 +12400,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12509,14 +12514,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -12538,10 +12543,10 @@
         <v>130</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>133</v>
@@ -12596,7 +12601,7 @@
         <v>75</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>76</v>
@@ -12625,10 +12630,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12651,13 +12656,13 @@
         <v>75</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -12708,7 +12713,7 @@
         <v>75</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>84</v>
@@ -12729,7 +12734,7 @@
         <v>75</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>75</v>
@@ -12737,10 +12742,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12763,13 +12768,13 @@
         <v>75</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -12820,7 +12825,7 @@
         <v>75</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>84</v>
@@ -12841,7 +12846,7 @@
         <v>75</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>75</v>
@@ -12849,10 +12854,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12875,13 +12880,13 @@
         <v>75</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -12932,7 +12937,7 @@
         <v>75</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>76</v>
@@ -12953,7 +12958,7 @@
         <v>75</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>75</v>
@@ -12961,10 +12966,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12987,19 +12992,19 @@
         <v>85</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>75</v>
@@ -13048,7 +13053,7 @@
         <v>75</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>76</v>
@@ -13069,7 +13074,7 @@
         <v>75</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>75</v>
@@ -13077,10 +13082,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13189,10 +13194,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13303,10 +13308,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13332,13 +13337,13 @@
         <v>149</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -13388,7 +13393,7 @@
         <v>75</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>76</v>
@@ -13397,7 +13402,7 @@
         <v>84</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>96</v>
@@ -13417,10 +13422,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13446,13 +13451,13 @@
         <v>98</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13481,10 +13486,10 @@
         <v>176</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>75</v>
@@ -13502,7 +13507,7 @@
         <v>75</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>76</v>
@@ -13531,10 +13536,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13560,13 +13565,13 @@
         <v>142</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -13616,7 +13621,7 @@
         <v>75</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>76</v>
@@ -13637,7 +13642,7 @@
         <v>75</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>75</v>
@@ -13645,10 +13650,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13674,13 +13679,13 @@
         <v>149</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -13691,7 +13696,7 @@
         <v>75</v>
       </c>
       <c r="S101" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="T101" t="s" s="2">
         <v>75</v>
@@ -13730,7 +13735,7 @@
         <v>75</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>76</v>
@@ -13745,7 +13750,7 @@
         <v>96</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>75</v>
@@ -13759,10 +13764,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13785,17 +13790,17 @@
         <v>75</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>75</v>
@@ -13844,7 +13849,7 @@
         <v>75</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>76</v>
@@ -13865,7 +13870,7 @@
         <v>75</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>75</v>
@@ -13873,10 +13878,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13899,16 +13904,16 @@
         <v>75</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -13958,7 +13963,7 @@
         <v>75</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>76</v>
@@ -13979,7 +13984,7 @@
         <v>75</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>75</v>
@@ -13987,10 +13992,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14099,10 +14104,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14213,14 +14218,14 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -14242,10 +14247,10 @@
         <v>130</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>133</v>
@@ -14300,7 +14305,7 @@
         <v>75</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>76</v>
@@ -14329,10 +14334,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14358,10 +14363,10 @@
         <v>104</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -14391,10 +14396,10 @@
         <v>165</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>75</v>
@@ -14412,7 +14417,7 @@
         <v>75</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>76</v>
@@ -14433,7 +14438,7 @@
         <v>75</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>75</v>
@@ -14441,10 +14446,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14467,13 +14472,13 @@
         <v>75</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -14524,7 +14529,7 @@
         <v>75</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>76</v>
@@ -14545,7 +14550,7 @@
         <v>75</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>75</v>
@@ -14553,10 +14558,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14579,13 +14584,13 @@
         <v>75</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -14636,7 +14641,7 @@
         <v>75</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>76</v>
@@ -14657,7 +14662,7 @@
         <v>75</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>75</v>
@@ -14665,10 +14670,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14691,13 +14696,13 @@
         <v>75</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -14748,7 +14753,7 @@
         <v>75</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>76</v>
@@ -14769,7 +14774,7 @@
         <v>75</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>75</v>
@@ -14777,10 +14782,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14806,10 +14811,10 @@
         <v>149</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -14860,7 +14865,7 @@
         <v>75</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>76</v>
@@ -14889,10 +14894,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14915,17 +14920,17 @@
         <v>75</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>75</v>
@@ -14974,7 +14979,7 @@
         <v>75</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>76</v>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -7171,7 +7171,7 @@
         <v>84</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>75</v>
@@ -7401,7 +7401,7 @@
         <v>84</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>75</v>
@@ -8543,7 +8543,7 @@
         <v>84</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>75</v>
@@ -8773,7 +8773,7 @@
         <v>84</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>75</v>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Location.xlsx
+++ b/docs/StructureDefinition-Location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
